--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R659e733181f64b88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R587df9384cb64057"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -195,102 +195,96 @@
       </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
@@ -298,45 +292,62 @@
       </x:extLst>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -572,462 +583,462 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="31" t="str">
+      <x:c r="A1" s="33" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="12" t="str">
+      <x:c r="B1" s="14" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="12" t="str">
+      <x:c r="C1" s="14" t="str">
         <x:v>flags</x:v>
       </x:c>
-      <x:c r="D1" s="12" t="str">
+      <x:c r="D1" s="14" t="str">
         <x:v>unique</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="E1" s="14" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="F1" s="12" t="str">
+      <x:c r="F1" s="14" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="G1" s="12" t="str">
+      <x:c r="G1" s="14" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="H1" s="12" t="str">
+      <x:c r="H1" s="14" t="str">
         <x:v>*items</x:v>
       </x:c>
-      <x:c r="I1" s="12"/>
-      <x:c r="J1" s="12"/>
-      <x:c r="K1" s="12"/>
-      <x:c r="L1" s="13"/>
+      <x:c r="I1" s="14"/>
+      <x:c r="J1" s="14"/>
+      <x:c r="K1" s="14"/>
+      <x:c r="L1" s="15"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="35" t="str">
+      <x:c r="A2" s="37" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B2" s="16"/>
-      <x:c r="C2" s="16"/>
-      <x:c r="D2" s="16"/>
-      <x:c r="E2" s="16"/>
-      <x:c r="F2" s="16"/>
-      <x:c r="G2" s="16"/>
-      <x:c r="H2" s="16" t="str">
+      <x:c r="B2" s="18"/>
+      <x:c r="C2" s="18"/>
+      <x:c r="D2" s="18"/>
+      <x:c r="E2" s="18"/>
+      <x:c r="F2" s="18"/>
+      <x:c r="G2" s="18"/>
+      <x:c r="H2" s="18" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="I2" s="16" t="str">
+      <x:c r="I2" s="18" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="J2" s="16" t="str">
+      <x:c r="J2" s="18" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="K2" s="16" t="str">
+      <x:c r="K2" s="18" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="L2" s="16" t="str">
+      <x:c r="L2" s="18" t="str">
         <x:v>tags</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="36" t="str">
+      <x:c r="A3" s="38" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="18" t="str">
+      <x:c r="B3" s="20" t="str">
         <x:v>完整枚举名</x:v>
       </x:c>
-      <x:c r="C3" s="18" t="str">
+      <x:c r="C3" s="20" t="str">
         <x:v>位标记</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str">
+      <x:c r="D3" s="20" t="str">
         <x:v>值唯一</x:v>
       </x:c>
-      <x:c r="E3" s="18" t="str">
+      <x:c r="E3" s="20" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="F3" s="18" t="str">
+      <x:c r="F3" s="20" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="str">
+      <x:c r="G3" s="20" t="str">
         <x:v>标签</x:v>
       </x:c>
-      <x:c r="H3" s="18" t="str">
+      <x:c r="H3" s="20" t="str">
         <x:v>枚举项</x:v>
       </x:c>
-      <x:c r="I3" s="18" t="str">
+      <x:c r="I3" s="20" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="J3" s="18" t="str">
+      <x:c r="J3" s="20" t="str">
         <x:v>值</x:v>
       </x:c>
-      <x:c r="K3" s="18" t="str">
+      <x:c r="K3" s="20" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="L3" s="18" t="str">
+      <x:c r="L3" s="20" t="str">
         <x:v>标签</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="37"/>
-      <x:c r="B4" s="28" t="str">
+      <x:c r="A4" s="39"/>
+      <x:c r="B4" s="30" t="str">
         <x:v>EResourceType</x:v>
       </x:c>
-      <x:c r="C4" s="29" t="b">
+      <x:c r="C4" s="31" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="29" t="b">
+      <x:c r="D4" s="31" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" s="28"/>
-      <x:c r="F4" s="28"/>
-      <x:c r="G4" s="28"/>
-      <x:c r="H4" s="28" t="str">
+      <x:c r="E4" s="30"/>
+      <x:c r="F4" s="30"/>
+      <x:c r="G4" s="30"/>
+      <x:c r="H4" s="30" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="I4" s="28"/>
-      <x:c r="J4" s="28" t="n">
+      <x:c r="I4" s="30"/>
+      <x:c r="J4" s="30" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K4" s="28" t="str">
+      <x:c r="K4" s="30" t="str">
         <x:v>未知</x:v>
       </x:c>
-      <x:c r="L4" s="30"/>
+      <x:c r="L4" s="32"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="38"/>
-      <x:c r="B5" s="38"/>
-      <x:c r="C5" s="38"/>
-      <x:c r="D5" s="38"/>
-      <x:c r="E5" s="38"/>
-      <x:c r="F5" s="38"/>
-      <x:c r="G5" s="38"/>
-      <x:c r="H5" s="38" t="str">
+      <x:c r="A5" s="40"/>
+      <x:c r="B5" s="40"/>
+      <x:c r="C5" s="40"/>
+      <x:c r="D5" s="40"/>
+      <x:c r="E5" s="40"/>
+      <x:c r="F5" s="40"/>
+      <x:c r="G5" s="40"/>
+      <x:c r="H5" s="40" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="I5" s="38"/>
-      <x:c r="J5" s="38" t="n">
+      <x:c r="I5" s="40"/>
+      <x:c r="J5" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K5" s="38" t="str">
+      <x:c r="K5" s="40" t="str">
         <x:v>ANI动画</x:v>
       </x:c>
-      <x:c r="L5" s="38"/>
+      <x:c r="L5" s="40"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="39"/>
-      <x:c r="B6" s="39"/>
-      <x:c r="C6" s="39"/>
-      <x:c r="D6" s="39"/>
-      <x:c r="E6" s="39"/>
-      <x:c r="F6" s="39"/>
-      <x:c r="G6" s="39"/>
-      <x:c r="H6" s="39" t="str">
+      <x:c r="A6" s="41"/>
+      <x:c r="B6" s="41"/>
+      <x:c r="C6" s="41"/>
+      <x:c r="D6" s="41"/>
+      <x:c r="E6" s="41"/>
+      <x:c r="F6" s="41"/>
+      <x:c r="G6" s="41"/>
+      <x:c r="H6" s="41" t="str">
         <x:v>Texture</x:v>
       </x:c>
-      <x:c r="I6" s="39"/>
-      <x:c r="J6" s="39" t="n">
+      <x:c r="I6" s="41"/>
+      <x:c r="J6" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K6" s="39" t="str">
+      <x:c r="K6" s="41" t="str">
         <x:v>纹理</x:v>
       </x:c>
-      <x:c r="L6" s="39"/>
+      <x:c r="L6" s="41"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="39"/>
-      <x:c r="B7" s="39"/>
-      <x:c r="C7" s="39"/>
-      <x:c r="D7" s="39"/>
-      <x:c r="E7" s="39"/>
-      <x:c r="F7" s="39"/>
-      <x:c r="G7" s="39"/>
-      <x:c r="H7" s="39" t="str">
+      <x:c r="A7" s="41"/>
+      <x:c r="B7" s="41"/>
+      <x:c r="C7" s="41"/>
+      <x:c r="D7" s="41"/>
+      <x:c r="E7" s="41"/>
+      <x:c r="F7" s="41"/>
+      <x:c r="G7" s="41"/>
+      <x:c r="H7" s="41" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="I7" s="39"/>
-      <x:c r="J7" s="39" t="n">
+      <x:c r="I7" s="41"/>
+      <x:c r="J7" s="41" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K7" s="39" t="str">
+      <x:c r="K7" s="41" t="str">
         <x:v>音频</x:v>
       </x:c>
-      <x:c r="L7" s="39"/>
+      <x:c r="L7" s="41"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="39"/>
-      <x:c r="B8" s="39"/>
-      <x:c r="C8" s="39"/>
-      <x:c r="D8" s="39"/>
-      <x:c r="E8" s="39"/>
-      <x:c r="F8" s="39"/>
-      <x:c r="G8" s="39"/>
-      <x:c r="H8" s="39" t="str">
+      <x:c r="A8" s="41"/>
+      <x:c r="B8" s="41"/>
+      <x:c r="C8" s="41"/>
+      <x:c r="D8" s="41"/>
+      <x:c r="E8" s="41"/>
+      <x:c r="F8" s="41"/>
+      <x:c r="G8" s="41"/>
+      <x:c r="H8" s="41" t="str">
         <x:v>MapData</x:v>
       </x:c>
-      <x:c r="I8" s="39"/>
-      <x:c r="J8" s="39" t="n">
+      <x:c r="I8" s="41"/>
+      <x:c r="J8" s="41" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K8" s="39" t="str">
+      <x:c r="K8" s="41" t="str">
         <x:v>地图数据</x:v>
       </x:c>
-      <x:c r="L8" s="39"/>
+      <x:c r="L8" s="41"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="39"/>
-      <x:c r="B9" s="39"/>
-      <x:c r="C9" s="39"/>
-      <x:c r="D9" s="39"/>
-      <x:c r="E9" s="39"/>
-      <x:c r="F9" s="39"/>
-      <x:c r="G9" s="39"/>
-      <x:c r="H9" s="39" t="str">
+      <x:c r="A9" s="41"/>
+      <x:c r="B9" s="41"/>
+      <x:c r="C9" s="41"/>
+      <x:c r="D9" s="41"/>
+      <x:c r="E9" s="41"/>
+      <x:c r="F9" s="41"/>
+      <x:c r="G9" s="41"/>
+      <x:c r="H9" s="41" t="str">
         <x:v>Binary</x:v>
       </x:c>
-      <x:c r="I9" s="39"/>
-      <x:c r="J9" s="39" t="n">
+      <x:c r="I9" s="41"/>
+      <x:c r="J9" s="41" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K9" s="39" t="str">
+      <x:c r="K9" s="41" t="str">
         <x:v>其他二进制</x:v>
       </x:c>
-      <x:c r="L9" s="39"/>
+      <x:c r="L9" s="41"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="39"/>
-      <x:c r="B10" s="39" t="str">
+      <x:c r="A10" s="41"/>
+      <x:c r="B10" s="41" t="str">
         <x:v>EVisualCategory</x:v>
       </x:c>
-      <x:c r="C10" s="40" t="b">
+      <x:c r="C10" s="42" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="40" t="b">
+      <x:c r="D10" s="42" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E10" s="39"/>
-      <x:c r="F10" s="39"/>
-      <x:c r="G10" s="39"/>
-      <x:c r="H10" s="39" t="str">
+      <x:c r="E10" s="41"/>
+      <x:c r="F10" s="41"/>
+      <x:c r="G10" s="41"/>
+      <x:c r="H10" s="41" t="str">
         <x:v>Other</x:v>
       </x:c>
-      <x:c r="I10" s="39"/>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="I10" s="41"/>
+      <x:c r="J10" s="41" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="str">
+      <x:c r="K10" s="41" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L10" s="39"/>
+      <x:c r="L10" s="41"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="39"/>
-      <x:c r="B11" s="39"/>
-      <x:c r="C11" s="39"/>
-      <x:c r="D11" s="39"/>
-      <x:c r="E11" s="39"/>
-      <x:c r="F11" s="39"/>
-      <x:c r="G11" s="39"/>
-      <x:c r="H11" s="39" t="str">
+      <x:c r="A11" s="41"/>
+      <x:c r="B11" s="41"/>
+      <x:c r="C11" s="41"/>
+      <x:c r="D11" s="41"/>
+      <x:c r="E11" s="41"/>
+      <x:c r="F11" s="41"/>
+      <x:c r="G11" s="41"/>
+      <x:c r="H11" s="41" t="str">
         <x:v>Character</x:v>
       </x:c>
-      <x:c r="I11" s="39"/>
-      <x:c r="J11" s="39" t="n">
+      <x:c r="I11" s="41"/>
+      <x:c r="J11" s="41" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K11" s="39" t="str">
+      <x:c r="K11" s="41" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="L11" s="39"/>
+      <x:c r="L11" s="41"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="39"/>
-      <x:c r="B12" s="39"/>
-      <x:c r="C12" s="39"/>
-      <x:c r="D12" s="39"/>
-      <x:c r="E12" s="39"/>
-      <x:c r="F12" s="39"/>
-      <x:c r="G12" s="39"/>
-      <x:c r="H12" s="39" t="str">
+      <x:c r="A12" s="41"/>
+      <x:c r="B12" s="41"/>
+      <x:c r="C12" s="41"/>
+      <x:c r="D12" s="41"/>
+      <x:c r="E12" s="41"/>
+      <x:c r="F12" s="41"/>
+      <x:c r="G12" s="41"/>
+      <x:c r="H12" s="41" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="I12" s="39"/>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="I12" s="41"/>
+      <x:c r="J12" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="str">
+      <x:c r="K12" s="41" t="str">
         <x:v>怪物</x:v>
       </x:c>
-      <x:c r="L12" s="39"/>
+      <x:c r="L12" s="41"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="39"/>
-      <x:c r="B13" s="39"/>
-      <x:c r="C13" s="39"/>
-      <x:c r="D13" s="39"/>
-      <x:c r="E13" s="39"/>
-      <x:c r="F13" s="39"/>
-      <x:c r="G13" s="39"/>
-      <x:c r="H13" s="39" t="str">
+      <x:c r="A13" s="41"/>
+      <x:c r="B13" s="41"/>
+      <x:c r="C13" s="41"/>
+      <x:c r="D13" s="41"/>
+      <x:c r="E13" s="41"/>
+      <x:c r="F13" s="41"/>
+      <x:c r="G13" s="41"/>
+      <x:c r="H13" s="41" t="str">
         <x:v>Skill</x:v>
       </x:c>
-      <x:c r="I13" s="39"/>
-      <x:c r="J13" s="39" t="n">
+      <x:c r="I13" s="41"/>
+      <x:c r="J13" s="41" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K13" s="39" t="str">
+      <x:c r="K13" s="41" t="str">
         <x:v>技能</x:v>
       </x:c>
-      <x:c r="L13" s="39"/>
+      <x:c r="L13" s="41"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="39"/>
-      <x:c r="B14" s="39"/>
-      <x:c r="C14" s="39"/>
-      <x:c r="D14" s="39"/>
-      <x:c r="E14" s="39"/>
-      <x:c r="F14" s="39"/>
-      <x:c r="G14" s="39"/>
-      <x:c r="H14" s="39" t="str">
+      <x:c r="A14" s="41"/>
+      <x:c r="B14" s="41"/>
+      <x:c r="C14" s="41"/>
+      <x:c r="D14" s="41"/>
+      <x:c r="E14" s="41"/>
+      <x:c r="F14" s="41"/>
+      <x:c r="G14" s="41"/>
+      <x:c r="H14" s="41" t="str">
         <x:v>Map</x:v>
       </x:c>
-      <x:c r="I14" s="39"/>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="I14" s="41"/>
+      <x:c r="J14" s="41" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="str">
+      <x:c r="K14" s="41" t="str">
         <x:v>地图</x:v>
       </x:c>
-      <x:c r="L14" s="39"/>
+      <x:c r="L14" s="41"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="39"/>
-      <x:c r="B15" s="39" t="str">
+      <x:c r="A15" s="41"/>
+      <x:c r="B15" s="41" t="str">
         <x:v>EAnimationAction</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="b">
+      <x:c r="C15" s="42" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="b">
+      <x:c r="D15" s="42" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E15" s="39"/>
-      <x:c r="F15" s="39"/>
-      <x:c r="G15" s="39"/>
-      <x:c r="H15" s="39" t="str">
+      <x:c r="E15" s="41"/>
+      <x:c r="F15" s="41"/>
+      <x:c r="G15" s="41"/>
+      <x:c r="H15" s="41" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="I15" s="39"/>
-      <x:c r="J15" s="39" t="n">
+      <x:c r="I15" s="41"/>
+      <x:c r="J15" s="41" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="39" t="str">
+      <x:c r="K15" s="41" t="str">
         <x:v>尚未确认</x:v>
       </x:c>
-      <x:c r="L15" s="39"/>
+      <x:c r="L15" s="41"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="39"/>
-      <x:c r="B16" s="39"/>
-      <x:c r="C16" s="39"/>
-      <x:c r="D16" s="39"/>
-      <x:c r="E16" s="39"/>
-      <x:c r="F16" s="39"/>
-      <x:c r="G16" s="39"/>
-      <x:c r="H16" s="39" t="str">
+      <x:c r="A16" s="41"/>
+      <x:c r="B16" s="41"/>
+      <x:c r="C16" s="41"/>
+      <x:c r="D16" s="41"/>
+      <x:c r="E16" s="41"/>
+      <x:c r="F16" s="41"/>
+      <x:c r="G16" s="41"/>
+      <x:c r="H16" s="41" t="str">
         <x:v>Stand</x:v>
       </x:c>
-      <x:c r="I16" s="39"/>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="I16" s="41"/>
+      <x:c r="J16" s="41" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="str">
+      <x:c r="K16" s="41" t="str">
         <x:v>站立 fd</x:v>
       </x:c>
-      <x:c r="L16" s="39"/>
+      <x:c r="L16" s="41"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="39"/>
-      <x:c r="B17" s="39"/>
-      <x:c r="C17" s="39"/>
-      <x:c r="D17" s="39"/>
-      <x:c r="E17" s="39"/>
-      <x:c r="F17" s="39"/>
-      <x:c r="G17" s="39"/>
-      <x:c r="H17" s="39" t="str">
+      <x:c r="A17" s="41"/>
+      <x:c r="B17" s="41"/>
+      <x:c r="C17" s="41"/>
+      <x:c r="D17" s="41"/>
+      <x:c r="E17" s="41"/>
+      <x:c r="F17" s="41"/>
+      <x:c r="G17" s="41"/>
+      <x:c r="H17" s="41" t="str">
         <x:v>Move</x:v>
       </x:c>
-      <x:c r="I17" s="39"/>
-      <x:c r="J17" s="39" t="n">
+      <x:c r="I17" s="41"/>
+      <x:c r="J17" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K17" s="39" t="str">
+      <x:c r="K17" s="41" t="str">
         <x:v>移动 pb</x:v>
       </x:c>
-      <x:c r="L17" s="39"/>
+      <x:c r="L17" s="41"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="39"/>
-      <x:c r="B18" s="39" t="str">
+      <x:c r="A18" s="41"/>
+      <x:c r="B18" s="41" t="str">
         <x:v>EPerformanceKind</x:v>
       </x:c>
-      <x:c r="C18" s="40" t="b">
+      <x:c r="C18" s="42" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D18" s="40" t="b">
+      <x:c r="D18" s="42" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E18" s="39"/>
-      <x:c r="F18" s="39"/>
-      <x:c r="G18" s="39"/>
-      <x:c r="H18" s="39" t="str">
+      <x:c r="E18" s="41"/>
+      <x:c r="F18" s="41"/>
+      <x:c r="G18" s="41"/>
+      <x:c r="H18" s="41" t="str">
         <x:v>SameMonster</x:v>
       </x:c>
-      <x:c r="I18" s="39"/>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="I18" s="41"/>
+      <x:c r="J18" s="41" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="str">
+      <x:c r="K18" s="41" t="str">
         <x:v>同种怪物</x:v>
       </x:c>
-      <x:c r="L18" s="39"/>
+      <x:c r="L18" s="41"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="39"/>
-      <x:c r="B19" s="39"/>
-      <x:c r="C19" s="39"/>
-      <x:c r="D19" s="39"/>
-      <x:c r="E19" s="39"/>
-      <x:c r="F19" s="39"/>
-      <x:c r="G19" s="39"/>
-      <x:c r="H19" s="39" t="str">
+      <x:c r="A19" s="41"/>
+      <x:c r="B19" s="41"/>
+      <x:c r="C19" s="41"/>
+      <x:c r="D19" s="41"/>
+      <x:c r="E19" s="41"/>
+      <x:c r="F19" s="41"/>
+      <x:c r="G19" s="41"/>
+      <x:c r="H19" s="41" t="str">
         <x:v>MixedMonsters</x:v>
       </x:c>
-      <x:c r="I19" s="39"/>
-      <x:c r="J19" s="39" t="n">
+      <x:c r="I19" s="41"/>
+      <x:c r="J19" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K19" s="39" t="str">
+      <x:c r="K19" s="41" t="str">
         <x:v>混合怪物</x:v>
       </x:c>
-      <x:c r="L19" s="39"/>
+      <x:c r="L19" s="41"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="41"/>
-      <x:c r="B20" s="41"/>
-      <x:c r="C20" s="41"/>
-      <x:c r="D20" s="41"/>
-      <x:c r="E20" s="41"/>
-      <x:c r="F20" s="41"/>
-      <x:c r="G20" s="41"/>
-      <x:c r="H20" s="41" t="str">
+      <x:c r="A20" s="43"/>
+      <x:c r="B20" s="43"/>
+      <x:c r="C20" s="43"/>
+      <x:c r="D20" s="43"/>
+      <x:c r="E20" s="43"/>
+      <x:c r="F20" s="43"/>
+      <x:c r="G20" s="43"/>
+      <x:c r="H20" s="43" t="str">
         <x:v>MixedMonstersWithSkills</x:v>
       </x:c>
-      <x:c r="I20" s="41"/>
-      <x:c r="J20" s="41" t="n">
+      <x:c r="I20" s="43"/>
+      <x:c r="J20" s="43" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K20" s="41" t="str">
+      <x:c r="K20" s="43" t="str">
         <x:v>混合怪物与技能</x:v>
       </x:c>
-      <x:c r="L20" s="41"/>
+      <x:c r="L20" s="43"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R587df9384cb64057"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R808b12158c804c2e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -348,6 +348,31 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -950,7 +975,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K16" s="41" t="str">
-        <x:v>站立 fd</x:v>
+        <x:v>待机：主角 fd，怪物 zd</x:v>
       </x:c>
       <x:c r="L16" s="41"/>
     </x:row>
@@ -976,27 +1001,21 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41" t="str">
-        <x:v>EPerformanceKind</x:v>
-      </x:c>
-      <x:c r="C18" s="42" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="42" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B18" s="41"/>
+      <x:c r="C18" s="41"/>
+      <x:c r="D18" s="41"/>
       <x:c r="E18" s="41"/>
       <x:c r="F18" s="41"/>
       <x:c r="G18" s="41"/>
       <x:c r="H18" s="41" t="str">
-        <x:v>SameMonster</x:v>
+        <x:v>Unused</x:v>
       </x:c>
       <x:c r="I18" s="41"/>
       <x:c r="J18" s="41" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K18" s="41" t="str">
-        <x:v>同种怪物</x:v>
+        <x:v>本轮不使用的动作</x:v>
       </x:c>
       <x:c r="L18" s="41"/>
     </x:row>
@@ -1009,14 +1028,14 @@
       <x:c r="F19" s="41"/>
       <x:c r="G19" s="41"/>
       <x:c r="H19" s="41" t="str">
-        <x:v>MixedMonsters</x:v>
+        <x:v>Attack</x:v>
       </x:c>
       <x:c r="I19" s="41"/>
       <x:c r="J19" s="41" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K19" s="41" t="str">
-        <x:v>混合怪物</x:v>
+        <x:v>攻击 gj</x:v>
       </x:c>
       <x:c r="L19" s="41"/>
     </x:row>
@@ -1029,16 +1048,672 @@
       <x:c r="F20" s="43"/>
       <x:c r="G20" s="43"/>
       <x:c r="H20" s="43" t="str">
-        <x:v>MixedMonstersWithSkills</x:v>
+        <x:v>Hit</x:v>
       </x:c>
       <x:c r="I20" s="43"/>
       <x:c r="J20" s="43" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K20" s="43" t="str">
+        <x:v>被击 bj</x:v>
+      </x:c>
+      <x:c r="L20" s="43"/>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="46"/>
+      <x:c r="B21" s="46"/>
+      <x:c r="C21" s="46"/>
+      <x:c r="D21" s="46"/>
+      <x:c r="E21" s="46"/>
+      <x:c r="F21" s="46"/>
+      <x:c r="G21" s="46"/>
+      <x:c r="H21" s="46" t="str">
+        <x:v>Cast1</x:v>
+      </x:c>
+      <x:c r="I21" s="46"/>
+      <x:c r="J21" s="46" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K21" s="48" t="str">
+        <x:v>施法 sf1</x:v>
+      </x:c>
+      <x:c r="L21" s="46"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="46"/>
+      <x:c r="B22" s="46"/>
+      <x:c r="C22" s="46"/>
+      <x:c r="D22" s="46"/>
+      <x:c r="E22" s="46"/>
+      <x:c r="F22" s="46"/>
+      <x:c r="G22" s="46"/>
+      <x:c r="H22" s="46" t="str">
+        <x:v>Cast2</x:v>
+      </x:c>
+      <x:c r="I22" s="46"/>
+      <x:c r="J22" s="46" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K22" s="48" t="str">
+        <x:v>施法 sf2</x:v>
+      </x:c>
+      <x:c r="L22" s="46"/>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="46"/>
+      <x:c r="B23" s="46"/>
+      <x:c r="C23" s="46"/>
+      <x:c r="D23" s="46"/>
+      <x:c r="E23" s="46"/>
+      <x:c r="F23" s="46"/>
+      <x:c r="G23" s="46"/>
+      <x:c r="H23" s="46" t="str">
+        <x:v>Cast3</x:v>
+      </x:c>
+      <x:c r="I23" s="46"/>
+      <x:c r="J23" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K23" s="48" t="str">
+        <x:v>施法 sf3</x:v>
+      </x:c>
+      <x:c r="L23" s="46"/>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="46"/>
+      <x:c r="B24" s="46"/>
+      <x:c r="C24" s="46"/>
+      <x:c r="D24" s="46"/>
+      <x:c r="E24" s="46"/>
+      <x:c r="F24" s="46"/>
+      <x:c r="G24" s="46"/>
+      <x:c r="H24" s="46" t="str">
+        <x:v>Cast4</x:v>
+      </x:c>
+      <x:c r="I24" s="46"/>
+      <x:c r="J24" s="46" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K24" s="48" t="str">
+        <x:v>施法 sf4</x:v>
+      </x:c>
+      <x:c r="L24" s="46"/>
+    </x:row>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="46"/>
+      <x:c r="B25" s="46"/>
+      <x:c r="C25" s="46"/>
+      <x:c r="D25" s="46"/>
+      <x:c r="E25" s="46"/>
+      <x:c r="F25" s="46"/>
+      <x:c r="G25" s="46"/>
+      <x:c r="H25" s="46" t="str">
+        <x:v>Death</x:v>
+      </x:c>
+      <x:c r="I25" s="46"/>
+      <x:c r="J25" s="46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K25" s="48" t="str">
+        <x:v>死亡 sw</x:v>
+      </x:c>
+      <x:c r="L25" s="46"/>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="46"/>
+      <x:c r="B26" s="46" t="str">
+        <x:v>EPerformanceKind</x:v>
+      </x:c>
+      <x:c r="C26" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="47" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E26" s="46"/>
+      <x:c r="F26" s="46"/>
+      <x:c r="G26" s="46"/>
+      <x:c r="H26" s="46" t="str">
+        <x:v>SameMonster</x:v>
+      </x:c>
+      <x:c r="I26" s="46"/>
+      <x:c r="J26" s="46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K26" s="48" t="str">
+        <x:v>同种怪物</x:v>
+      </x:c>
+      <x:c r="L26" s="46"/>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="46"/>
+      <x:c r="B27" s="46"/>
+      <x:c r="C27" s="46"/>
+      <x:c r="D27" s="46"/>
+      <x:c r="E27" s="46"/>
+      <x:c r="F27" s="46"/>
+      <x:c r="G27" s="46"/>
+      <x:c r="H27" s="46" t="str">
+        <x:v>MixedMonsters</x:v>
+      </x:c>
+      <x:c r="I27" s="46"/>
+      <x:c r="J27" s="46" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K27" s="48" t="str">
+        <x:v>混合怪物</x:v>
+      </x:c>
+      <x:c r="L27" s="46"/>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="46"/>
+      <x:c r="B28" s="46"/>
+      <x:c r="C28" s="46"/>
+      <x:c r="D28" s="46"/>
+      <x:c r="E28" s="46"/>
+      <x:c r="F28" s="46"/>
+      <x:c r="G28" s="46"/>
+      <x:c r="H28" s="46" t="str">
+        <x:v>MixedMonstersWithSkills</x:v>
+      </x:c>
+      <x:c r="I28" s="46"/>
+      <x:c r="J28" s="46" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K20" s="43" t="str">
+      <x:c r="K28" s="48" t="str">
         <x:v>混合怪物与技能</x:v>
       </x:c>
-      <x:c r="L20" s="43"/>
+      <x:c r="L28" s="46"/>
+    </x:row>
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="46"/>
+      <x:c r="B29" s="46"/>
+      <x:c r="C29" s="46"/>
+      <x:c r="D29" s="46"/>
+      <x:c r="E29" s="46"/>
+      <x:c r="F29" s="46"/>
+      <x:c r="G29" s="46"/>
+      <x:c r="H29" s="46" t="str">
+        <x:v>Combat</x:v>
+      </x:c>
+      <x:c r="I29" s="46"/>
+      <x:c r="J29" s="46" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K29" s="48" t="str">
+        <x:v>完整战斗测试</x:v>
+      </x:c>
+      <x:c r="L29" s="46"/>
+    </x:row>
+    <x:row r="30" ht="28" customHeight="1">
+      <x:c r="A30" s="46"/>
+      <x:c r="B30" s="46" t="str">
+        <x:v>EAttributeType</x:v>
+      </x:c>
+      <x:c r="C30" s="47" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="47" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E30" s="46"/>
+      <x:c r="F30" s="46"/>
+      <x:c r="G30" s="46"/>
+      <x:c r="H30" s="46" t="str">
+        <x:v>MaxHealth</x:v>
+      </x:c>
+      <x:c r="I30" s="46"/>
+      <x:c r="J30" s="46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K30" s="48" t="str">
+        <x:v>最大生命</x:v>
+      </x:c>
+      <x:c r="L30" s="46"/>
+    </x:row>
+    <x:row r="31" ht="28" customHeight="1">
+      <x:c r="A31" s="46"/>
+      <x:c r="B31" s="46"/>
+      <x:c r="C31" s="46"/>
+      <x:c r="D31" s="46"/>
+      <x:c r="E31" s="46"/>
+      <x:c r="F31" s="46"/>
+      <x:c r="G31" s="46"/>
+      <x:c r="H31" s="46" t="str">
+        <x:v>Attack</x:v>
+      </x:c>
+      <x:c r="I31" s="46"/>
+      <x:c r="J31" s="46" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K31" s="48" t="str">
+        <x:v>攻击</x:v>
+      </x:c>
+      <x:c r="L31" s="46"/>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="A32" s="46"/>
+      <x:c r="B32" s="46"/>
+      <x:c r="C32" s="46"/>
+      <x:c r="D32" s="46"/>
+      <x:c r="E32" s="46"/>
+      <x:c r="F32" s="46"/>
+      <x:c r="G32" s="46"/>
+      <x:c r="H32" s="46" t="str">
+        <x:v>Defense</x:v>
+      </x:c>
+      <x:c r="I32" s="46"/>
+      <x:c r="J32" s="46" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K32" s="48" t="str">
+        <x:v>防御</x:v>
+      </x:c>
+      <x:c r="L32" s="46"/>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
+      <x:c r="A33" s="46"/>
+      <x:c r="B33" s="46"/>
+      <x:c r="C33" s="46"/>
+      <x:c r="D33" s="46"/>
+      <x:c r="E33" s="46"/>
+      <x:c r="F33" s="46"/>
+      <x:c r="G33" s="46"/>
+      <x:c r="H33" s="46" t="str">
+        <x:v>MoveSpeed</x:v>
+      </x:c>
+      <x:c r="I33" s="46"/>
+      <x:c r="J33" s="46" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K33" s="48" t="str">
+        <x:v>移动速度</x:v>
+      </x:c>
+      <x:c r="L33" s="46"/>
+    </x:row>
+    <x:row r="34" ht="28" customHeight="1">
+      <x:c r="A34" s="46"/>
+      <x:c r="B34" s="46"/>
+      <x:c r="C34" s="46"/>
+      <x:c r="D34" s="46"/>
+      <x:c r="E34" s="46"/>
+      <x:c r="F34" s="46"/>
+      <x:c r="G34" s="46"/>
+      <x:c r="H34" s="46" t="str">
+        <x:v>AttackSpeedMultiplier</x:v>
+      </x:c>
+      <x:c r="I34" s="46"/>
+      <x:c r="J34" s="46" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K34" s="48" t="str">
+        <x:v>攻速倍率</x:v>
+      </x:c>
+      <x:c r="L34" s="46"/>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="46"/>
+      <x:c r="B35" s="46"/>
+      <x:c r="C35" s="46"/>
+      <x:c r="D35" s="46"/>
+      <x:c r="E35" s="46"/>
+      <x:c r="F35" s="46"/>
+      <x:c r="G35" s="46"/>
+      <x:c r="H35" s="46" t="str">
+        <x:v>DefenseParameter</x:v>
+      </x:c>
+      <x:c r="I35" s="46"/>
+      <x:c r="J35" s="46" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K35" s="48" t="str">
+        <x:v>防御参数</x:v>
+      </x:c>
+      <x:c r="L35" s="46"/>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="A36" s="46"/>
+      <x:c r="B36" s="46"/>
+      <x:c r="C36" s="46"/>
+      <x:c r="D36" s="46"/>
+      <x:c r="E36" s="46"/>
+      <x:c r="F36" s="46"/>
+      <x:c r="G36" s="46"/>
+      <x:c r="H36" s="46" t="str">
+        <x:v>Hit</x:v>
+      </x:c>
+      <x:c r="I36" s="46"/>
+      <x:c r="J36" s="46" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K36" s="48" t="str">
+        <x:v>命中值</x:v>
+      </x:c>
+      <x:c r="L36" s="46"/>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="A37" s="46"/>
+      <x:c r="B37" s="46"/>
+      <x:c r="C37" s="46"/>
+      <x:c r="D37" s="46"/>
+      <x:c r="E37" s="46"/>
+      <x:c r="F37" s="46"/>
+      <x:c r="G37" s="46"/>
+      <x:c r="H37" s="46" t="str">
+        <x:v>Evasion</x:v>
+      </x:c>
+      <x:c r="I37" s="46"/>
+      <x:c r="J37" s="46" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K37" s="48" t="str">
+        <x:v>闪避值</x:v>
+      </x:c>
+      <x:c r="L37" s="46"/>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" s="46"/>
+      <x:c r="B38" s="46"/>
+      <x:c r="C38" s="46"/>
+      <x:c r="D38" s="46"/>
+      <x:c r="E38" s="46"/>
+      <x:c r="F38" s="46"/>
+      <x:c r="G38" s="46"/>
+      <x:c r="H38" s="46" t="str">
+        <x:v>HitParameter</x:v>
+      </x:c>
+      <x:c r="I38" s="46"/>
+      <x:c r="J38" s="46" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K38" s="48" t="str">
+        <x:v>命中参数</x:v>
+      </x:c>
+      <x:c r="L38" s="46"/>
+    </x:row>
+    <x:row r="39" ht="28" customHeight="1">
+      <x:c r="A39" s="46"/>
+      <x:c r="B39" s="46"/>
+      <x:c r="C39" s="46"/>
+      <x:c r="D39" s="46"/>
+      <x:c r="E39" s="46"/>
+      <x:c r="F39" s="46"/>
+      <x:c r="G39" s="46"/>
+      <x:c r="H39" s="46" t="str">
+        <x:v>EvasionParameter</x:v>
+      </x:c>
+      <x:c r="I39" s="46"/>
+      <x:c r="J39" s="46" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K39" s="48" t="str">
+        <x:v>闪避参数</x:v>
+      </x:c>
+      <x:c r="L39" s="46"/>
+    </x:row>
+    <x:row r="40" ht="28" customHeight="1">
+      <x:c r="A40" s="46"/>
+      <x:c r="B40" s="46"/>
+      <x:c r="C40" s="46"/>
+      <x:c r="D40" s="46"/>
+      <x:c r="E40" s="46"/>
+      <x:c r="F40" s="46"/>
+      <x:c r="G40" s="46"/>
+      <x:c r="H40" s="46" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="I40" s="46"/>
+      <x:c r="J40" s="46" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K40" s="48" t="str">
+        <x:v>暴击值</x:v>
+      </x:c>
+      <x:c r="L40" s="46"/>
+    </x:row>
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" s="46"/>
+      <x:c r="B41" s="46"/>
+      <x:c r="C41" s="46"/>
+      <x:c r="D41" s="46"/>
+      <x:c r="E41" s="46"/>
+      <x:c r="F41" s="46"/>
+      <x:c r="G41" s="46"/>
+      <x:c r="H41" s="46" t="str">
+        <x:v>CriticalResistance</x:v>
+      </x:c>
+      <x:c r="I41" s="46"/>
+      <x:c r="J41" s="46" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K41" s="48" t="str">
+        <x:v>抗暴值</x:v>
+      </x:c>
+      <x:c r="L41" s="46"/>
+    </x:row>
+    <x:row r="42" ht="28" customHeight="1">
+      <x:c r="A42" s="46"/>
+      <x:c r="B42" s="46"/>
+      <x:c r="C42" s="46"/>
+      <x:c r="D42" s="46"/>
+      <x:c r="E42" s="46"/>
+      <x:c r="F42" s="46"/>
+      <x:c r="G42" s="46"/>
+      <x:c r="H42" s="46" t="str">
+        <x:v>CriticalParameter</x:v>
+      </x:c>
+      <x:c r="I42" s="46"/>
+      <x:c r="J42" s="46" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K42" s="48" t="str">
+        <x:v>暴击参数</x:v>
+      </x:c>
+      <x:c r="L42" s="46"/>
+    </x:row>
+    <x:row r="43" ht="28" customHeight="1">
+      <x:c r="A43" s="46"/>
+      <x:c r="B43" s="46"/>
+      <x:c r="C43" s="46"/>
+      <x:c r="D43" s="46"/>
+      <x:c r="E43" s="46"/>
+      <x:c r="F43" s="46"/>
+      <x:c r="G43" s="46"/>
+      <x:c r="H43" s="46" t="str">
+        <x:v>CriticalResistanceParameter</x:v>
+      </x:c>
+      <x:c r="I43" s="46"/>
+      <x:c r="J43" s="46" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K43" s="48" t="str">
+        <x:v>抗暴参数</x:v>
+      </x:c>
+      <x:c r="L43" s="46"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44"/>
+      <x:c r="B44" t="str">
+        <x:v>EAttributeValueKind</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
+      <x:c r="G44"/>
+      <x:c r="H44" t="str">
+        <x:v>Integer</x:v>
+      </x:c>
+      <x:c r="I44"/>
+      <x:c r="J44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K44" t="str">
+        <x:v>整数</x:v>
+      </x:c>
+      <x:c r="L44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45"/>
+      <x:c r="B45"/>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+      <x:c r="G45"/>
+      <x:c r="H45" t="str">
+        <x:v>Real</x:v>
+      </x:c>
+      <x:c r="I45"/>
+      <x:c r="J45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K45" t="str">
+        <x:v>实数</x:v>
+      </x:c>
+      <x:c r="L45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46"/>
+      <x:c r="B46" t="str">
+        <x:v>ESkillDeliveryType</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
+      <x:c r="G46"/>
+      <x:c r="H46" t="str">
+        <x:v>Projectile</x:v>
+      </x:c>
+      <x:c r="I46"/>
+      <x:c r="J46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>直线弹丸</x:v>
+      </x:c>
+      <x:c r="L46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47"/>
+      <x:c r="B47"/>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
+      <x:c r="H47" t="str">
+        <x:v>Melee</x:v>
+      </x:c>
+      <x:c r="I47"/>
+      <x:c r="J47" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K47" t="str">
+        <x:v>近战</x:v>
+      </x:c>
+      <x:c r="L47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48"/>
+      <x:c r="B48" t="str">
+        <x:v>ETestHealthPolicy</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D48" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
+      <x:c r="G48"/>
+      <x:c r="H48" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I48"/>
+      <x:c r="J48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K48" t="str">
+        <x:v>正常生命</x:v>
+      </x:c>
+      <x:c r="L48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49"/>
+      <x:c r="C49"/>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49"/>
+      <x:c r="G49"/>
+      <x:c r="H49" t="str">
+        <x:v>RestoreAfterDamage</x:v>
+      </x:c>
+      <x:c r="I49"/>
+      <x:c r="J49" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K49" t="str">
+        <x:v>结算正数扣血后恢复测试玩家生命</x:v>
+      </x:c>
+      <x:c r="L49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50" t="str">
+        <x:v>ETestInputPolicy</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50"/>
+      <x:c r="F50"/>
+      <x:c r="G50"/>
+      <x:c r="H50" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="I50"/>
+      <x:c r="J50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>玩家操作</x:v>
+      </x:c>
+      <x:c r="L50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
+      <x:c r="G51"/>
+      <x:c r="H51" t="str">
+        <x:v>Stationary</x:v>
+      </x:c>
+      <x:c r="I51"/>
+      <x:c r="J51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K51" t="str">
+        <x:v>玩家静止</x:v>
+      </x:c>
+      <x:c r="L51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R808b12158c804c2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R19f691d8a10c4d07"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,8 +59,68 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -92,8 +152,28 @@
         <x:fgColor rgb="FF64748B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="11">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -173,11 +253,25 @@
         <x:color rgb="FFE5E7EB"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="49">
+  <x:cellXfs count="101">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -373,6 +467,214 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -593,1127 +895,1479 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="28" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="29" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="8" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="8" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="8" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="33" t="str">
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="70" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="14" t="str">
+      <x:c r="B1" s="70" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="14" t="str">
+      <x:c r="C1" s="70" t="str">
         <x:v>flags</x:v>
       </x:c>
-      <x:c r="D1" s="14" t="str">
+      <x:c r="D1" s="70" t="str">
         <x:v>unique</x:v>
       </x:c>
-      <x:c r="E1" s="14" t="str">
+      <x:c r="E1" s="70" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="F1" s="14" t="str">
+      <x:c r="F1" s="70" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="G1" s="14" t="str">
+      <x:c r="G1" s="70" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="H1" s="14" t="str">
+      <x:c r="H1" s="70" t="str">
         <x:v>*items</x:v>
       </x:c>
-      <x:c r="I1" s="14"/>
-      <x:c r="J1" s="14"/>
-      <x:c r="K1" s="14"/>
-      <x:c r="L1" s="15"/>
-    </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="37" t="str">
+      <x:c r="I1" s="70"/>
+      <x:c r="J1" s="70"/>
+      <x:c r="K1" s="70"/>
+      <x:c r="L1" s="70"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="72" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B2" s="18"/>
-      <x:c r="C2" s="18"/>
-      <x:c r="D2" s="18"/>
-      <x:c r="E2" s="18"/>
-      <x:c r="F2" s="18"/>
-      <x:c r="G2" s="18"/>
-      <x:c r="H2" s="18" t="str">
+      <x:c r="B2" s="72"/>
+      <x:c r="C2" s="72"/>
+      <x:c r="D2" s="72"/>
+      <x:c r="E2" s="72"/>
+      <x:c r="F2" s="72"/>
+      <x:c r="G2" s="72"/>
+      <x:c r="H2" s="72" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="I2" s="18" t="str">
+      <x:c r="I2" s="72" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="J2" s="18" t="str">
+      <x:c r="J2" s="72" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="K2" s="18" t="str">
+      <x:c r="K2" s="72" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="L2" s="18" t="str">
+      <x:c r="L2" s="72" t="str">
         <x:v>tags</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="38" t="str">
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="75" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="20" t="str">
+      <x:c r="B3" s="76" t="str">
         <x:v>完整枚举名</x:v>
       </x:c>
-      <x:c r="C3" s="20" t="str">
+      <x:c r="C3" s="76" t="str">
         <x:v>位标记</x:v>
       </x:c>
-      <x:c r="D3" s="20" t="str">
+      <x:c r="D3" s="76" t="str">
         <x:v>值唯一</x:v>
       </x:c>
-      <x:c r="E3" s="20" t="str">
+      <x:c r="E3" s="76" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="F3" s="20" t="str">
+      <x:c r="F3" s="76" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="G3" s="20" t="str">
+      <x:c r="G3" s="76" t="str">
         <x:v>标签</x:v>
       </x:c>
-      <x:c r="H3" s="20" t="str">
+      <x:c r="H3" s="76" t="str">
         <x:v>枚举项</x:v>
       </x:c>
-      <x:c r="I3" s="20" t="str">
+      <x:c r="I3" s="76" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="J3" s="20" t="str">
+      <x:c r="J3" s="76" t="str">
         <x:v>值</x:v>
       </x:c>
-      <x:c r="K3" s="20" t="str">
+      <x:c r="K3" s="76" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="L3" s="20" t="str">
+      <x:c r="L3" s="76" t="str">
         <x:v>标签</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="39"/>
-      <x:c r="B4" s="30" t="str">
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="80"/>
+      <x:c r="B4" s="81" t="str">
         <x:v>EResourceType</x:v>
       </x:c>
-      <x:c r="C4" s="31" t="b">
+      <x:c r="C4" s="82" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="31" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="30"/>
-      <x:c r="F4" s="30"/>
-      <x:c r="G4" s="30"/>
-      <x:c r="H4" s="30" t="str">
+      <x:c r="D4" s="82" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="81"/>
+      <x:c r="F4" s="81"/>
+      <x:c r="G4" s="81"/>
+      <x:c r="H4" s="81" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="I4" s="30"/>
-      <x:c r="J4" s="30" t="n">
+      <x:c r="I4" s="81"/>
+      <x:c r="J4" s="81" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K4" s="30" t="str">
+      <x:c r="K4" s="81" t="str">
         <x:v>未知</x:v>
       </x:c>
-      <x:c r="L4" s="32"/>
+      <x:c r="L4" s="81"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="40"/>
-      <x:c r="B5" s="40"/>
-      <x:c r="C5" s="40"/>
-      <x:c r="D5" s="40"/>
-      <x:c r="E5" s="40"/>
-      <x:c r="F5" s="40"/>
-      <x:c r="G5" s="40"/>
-      <x:c r="H5" s="40" t="str">
+      <x:c r="A5" s="99"/>
+      <x:c r="B5" s="99"/>
+      <x:c r="C5" s="99"/>
+      <x:c r="D5" s="99"/>
+      <x:c r="E5" s="99"/>
+      <x:c r="F5" s="99"/>
+      <x:c r="G5" s="99"/>
+      <x:c r="H5" s="99" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="I5" s="40"/>
-      <x:c r="J5" s="40" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K5" s="40" t="str">
+      <x:c r="I5" s="99"/>
+      <x:c r="J5" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K5" s="99" t="str">
         <x:v>ANI动画</x:v>
       </x:c>
-      <x:c r="L5" s="40"/>
+      <x:c r="L5" s="99"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="41"/>
-      <x:c r="B6" s="41"/>
-      <x:c r="C6" s="41"/>
-      <x:c r="D6" s="41"/>
-      <x:c r="E6" s="41"/>
-      <x:c r="F6" s="41"/>
-      <x:c r="G6" s="41"/>
-      <x:c r="H6" s="41" t="str">
+      <x:c r="A6" s="99"/>
+      <x:c r="B6" s="99"/>
+      <x:c r="C6" s="99"/>
+      <x:c r="D6" s="99"/>
+      <x:c r="E6" s="99"/>
+      <x:c r="F6" s="99"/>
+      <x:c r="G6" s="99"/>
+      <x:c r="H6" s="99" t="str">
         <x:v>Texture</x:v>
       </x:c>
-      <x:c r="I6" s="41"/>
-      <x:c r="J6" s="41" t="n">
+      <x:c r="I6" s="99"/>
+      <x:c r="J6" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K6" s="41" t="str">
+      <x:c r="K6" s="99" t="str">
         <x:v>纹理</x:v>
       </x:c>
-      <x:c r="L6" s="41"/>
+      <x:c r="L6" s="99"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="41"/>
-      <x:c r="B7" s="41"/>
-      <x:c r="C7" s="41"/>
-      <x:c r="D7" s="41"/>
-      <x:c r="E7" s="41"/>
-      <x:c r="F7" s="41"/>
-      <x:c r="G7" s="41"/>
-      <x:c r="H7" s="41" t="str">
+      <x:c r="A7" s="99"/>
+      <x:c r="B7" s="99"/>
+      <x:c r="C7" s="99"/>
+      <x:c r="D7" s="99"/>
+      <x:c r="E7" s="99"/>
+      <x:c r="F7" s="99"/>
+      <x:c r="G7" s="99"/>
+      <x:c r="H7" s="99" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="I7" s="41"/>
-      <x:c r="J7" s="41" t="n">
+      <x:c r="I7" s="99"/>
+      <x:c r="J7" s="99" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K7" s="41" t="str">
+      <x:c r="K7" s="99" t="str">
         <x:v>音频</x:v>
       </x:c>
-      <x:c r="L7" s="41"/>
+      <x:c r="L7" s="99"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="41"/>
-      <x:c r="B8" s="41"/>
-      <x:c r="C8" s="41"/>
-      <x:c r="D8" s="41"/>
-      <x:c r="E8" s="41"/>
-      <x:c r="F8" s="41"/>
-      <x:c r="G8" s="41"/>
-      <x:c r="H8" s="41" t="str">
+      <x:c r="A8" s="99"/>
+      <x:c r="B8" s="99"/>
+      <x:c r="C8" s="99"/>
+      <x:c r="D8" s="99"/>
+      <x:c r="E8" s="99"/>
+      <x:c r="F8" s="99"/>
+      <x:c r="G8" s="99"/>
+      <x:c r="H8" s="99" t="str">
         <x:v>MapData</x:v>
       </x:c>
-      <x:c r="I8" s="41"/>
-      <x:c r="J8" s="41" t="n">
+      <x:c r="I8" s="99"/>
+      <x:c r="J8" s="99" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K8" s="41" t="str">
+      <x:c r="K8" s="99" t="str">
         <x:v>地图数据</x:v>
       </x:c>
-      <x:c r="L8" s="41"/>
+      <x:c r="L8" s="99"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="41"/>
-      <x:c r="B9" s="41"/>
-      <x:c r="C9" s="41"/>
-      <x:c r="D9" s="41"/>
-      <x:c r="E9" s="41"/>
-      <x:c r="F9" s="41"/>
-      <x:c r="G9" s="41"/>
-      <x:c r="H9" s="41" t="str">
+      <x:c r="A9" s="99"/>
+      <x:c r="B9" s="99"/>
+      <x:c r="C9" s="99"/>
+      <x:c r="D9" s="99"/>
+      <x:c r="E9" s="99"/>
+      <x:c r="F9" s="99"/>
+      <x:c r="G9" s="99"/>
+      <x:c r="H9" s="99" t="str">
         <x:v>Binary</x:v>
       </x:c>
-      <x:c r="I9" s="41"/>
-      <x:c r="J9" s="41" t="n">
+      <x:c r="I9" s="99"/>
+      <x:c r="J9" s="99" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K9" s="41" t="str">
+      <x:c r="K9" s="99" t="str">
         <x:v>其他二进制</x:v>
       </x:c>
-      <x:c r="L9" s="41"/>
+      <x:c r="L9" s="99"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="41"/>
-      <x:c r="B10" s="41" t="str">
+      <x:c r="A10" s="99"/>
+      <x:c r="B10" s="99"/>
+      <x:c r="C10" s="99"/>
+      <x:c r="D10" s="99"/>
+      <x:c r="E10" s="99"/>
+      <x:c r="F10" s="99"/>
+      <x:c r="G10" s="99"/>
+      <x:c r="H10" s="99" t="str">
+        <x:v>Prefab</x:v>
+      </x:c>
+      <x:c r="I10" s="99"/>
+      <x:c r="J10" s="99" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K10" s="99" t="str">
+        <x:v>Unity预制体</x:v>
+      </x:c>
+      <x:c r="L10" s="99"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="99"/>
+      <x:c r="B11" s="99"/>
+      <x:c r="C11" s="99"/>
+      <x:c r="D11" s="99"/>
+      <x:c r="E11" s="99"/>
+      <x:c r="F11" s="99"/>
+      <x:c r="G11" s="99"/>
+      <x:c r="H11" s="99" t="str">
+        <x:v>UnityAsset</x:v>
+      </x:c>
+      <x:c r="I11" s="99"/>
+      <x:c r="J11" s="99" t="str">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K11" s="99" t="str">
+        <x:v>其他Unity资产</x:v>
+      </x:c>
+      <x:c r="L11" s="99"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="99"/>
+      <x:c r="B12" s="99" t="str">
         <x:v>EVisualCategory</x:v>
       </x:c>
-      <x:c r="C10" s="42" t="b">
+      <x:c r="C12" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D10" s="42" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="41"/>
-      <x:c r="F10" s="41"/>
-      <x:c r="G10" s="41"/>
-      <x:c r="H10" s="41" t="str">
+      <x:c r="D12" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="99"/>
+      <x:c r="F12" s="99"/>
+      <x:c r="G12" s="99"/>
+      <x:c r="H12" s="99" t="str">
         <x:v>Other</x:v>
       </x:c>
-      <x:c r="I10" s="41"/>
-      <x:c r="J10" s="41" t="n">
+      <x:c r="I12" s="99"/>
+      <x:c r="J12" s="99" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="41" t="str">
+      <x:c r="K12" s="99" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L10" s="41"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="41"/>
-      <x:c r="B11" s="41"/>
-      <x:c r="C11" s="41"/>
-      <x:c r="D11" s="41"/>
-      <x:c r="E11" s="41"/>
-      <x:c r="F11" s="41"/>
-      <x:c r="G11" s="41"/>
-      <x:c r="H11" s="41" t="str">
+      <x:c r="L12" s="99"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="99"/>
+      <x:c r="B13" s="99"/>
+      <x:c r="C13" s="99"/>
+      <x:c r="D13" s="99"/>
+      <x:c r="E13" s="99"/>
+      <x:c r="F13" s="99"/>
+      <x:c r="G13" s="99"/>
+      <x:c r="H13" s="99" t="str">
         <x:v>Character</x:v>
       </x:c>
-      <x:c r="I11" s="41"/>
-      <x:c r="J11" s="41" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" s="41" t="str">
+      <x:c r="I13" s="99"/>
+      <x:c r="J13" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="99" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="L11" s="41"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="41"/>
-      <x:c r="B12" s="41"/>
-      <x:c r="C12" s="41"/>
-      <x:c r="D12" s="41"/>
-      <x:c r="E12" s="41"/>
-      <x:c r="F12" s="41"/>
-      <x:c r="G12" s="41"/>
-      <x:c r="H12" s="41" t="str">
+      <x:c r="L13" s="99"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="99"/>
+      <x:c r="B14" s="99"/>
+      <x:c r="C14" s="99"/>
+      <x:c r="D14" s="99"/>
+      <x:c r="E14" s="99"/>
+      <x:c r="F14" s="99"/>
+      <x:c r="G14" s="99"/>
+      <x:c r="H14" s="99" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="I12" s="41"/>
-      <x:c r="J12" s="41" t="n">
+      <x:c r="I14" s="99"/>
+      <x:c r="J14" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K12" s="41" t="str">
+      <x:c r="K14" s="99" t="str">
         <x:v>怪物</x:v>
       </x:c>
-      <x:c r="L12" s="41"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="41"/>
-      <x:c r="B13" s="41"/>
-      <x:c r="C13" s="41"/>
-      <x:c r="D13" s="41"/>
-      <x:c r="E13" s="41"/>
-      <x:c r="F13" s="41"/>
-      <x:c r="G13" s="41"/>
-      <x:c r="H13" s="41" t="str">
+      <x:c r="L14" s="99"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="99"/>
+      <x:c r="B15" s="99"/>
+      <x:c r="C15" s="99"/>
+      <x:c r="D15" s="99"/>
+      <x:c r="E15" s="99"/>
+      <x:c r="F15" s="99"/>
+      <x:c r="G15" s="99"/>
+      <x:c r="H15" s="99" t="str">
         <x:v>Skill</x:v>
       </x:c>
-      <x:c r="I13" s="41"/>
-      <x:c r="J13" s="41" t="n">
+      <x:c r="I15" s="99"/>
+      <x:c r="J15" s="99" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K13" s="41" t="str">
+      <x:c r="K15" s="99" t="str">
         <x:v>技能</x:v>
       </x:c>
-      <x:c r="L13" s="41"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="41"/>
-      <x:c r="B14" s="41"/>
-      <x:c r="C14" s="41"/>
-      <x:c r="D14" s="41"/>
-      <x:c r="E14" s="41"/>
-      <x:c r="F14" s="41"/>
-      <x:c r="G14" s="41"/>
-      <x:c r="H14" s="41" t="str">
+      <x:c r="L15" s="99"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="99"/>
+      <x:c r="B16" s="99"/>
+      <x:c r="C16" s="99"/>
+      <x:c r="D16" s="99"/>
+      <x:c r="E16" s="99"/>
+      <x:c r="F16" s="99"/>
+      <x:c r="G16" s="99"/>
+      <x:c r="H16" s="99" t="str">
         <x:v>Map</x:v>
       </x:c>
-      <x:c r="I14" s="41"/>
-      <x:c r="J14" s="41" t="n">
+      <x:c r="I16" s="99"/>
+      <x:c r="J16" s="99" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K14" s="41" t="str">
+      <x:c r="K16" s="99" t="str">
         <x:v>地图</x:v>
       </x:c>
-      <x:c r="L14" s="41"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="41"/>
-      <x:c r="B15" s="41" t="str">
+      <x:c r="L16" s="99"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="99"/>
+      <x:c r="B17" s="99" t="str">
         <x:v>EAnimationAction</x:v>
       </x:c>
-      <x:c r="C15" s="42" t="b">
+      <x:c r="C17" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D15" s="42" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" s="41"/>
-      <x:c r="F15" s="41"/>
-      <x:c r="G15" s="41"/>
-      <x:c r="H15" s="41" t="str">
+      <x:c r="D17" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="99"/>
+      <x:c r="F17" s="99"/>
+      <x:c r="G17" s="99"/>
+      <x:c r="H17" s="99" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="I15" s="41"/>
-      <x:c r="J15" s="41" t="n">
+      <x:c r="I17" s="99"/>
+      <x:c r="J17" s="99" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="41" t="str">
+      <x:c r="K17" s="99" t="str">
         <x:v>尚未确认</x:v>
       </x:c>
-      <x:c r="L15" s="41"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="41"/>
-      <x:c r="B16" s="41"/>
-      <x:c r="C16" s="41"/>
-      <x:c r="D16" s="41"/>
-      <x:c r="E16" s="41"/>
-      <x:c r="F16" s="41"/>
-      <x:c r="G16" s="41"/>
-      <x:c r="H16" s="41" t="str">
+      <x:c r="L17" s="99"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="99"/>
+      <x:c r="B18" s="99"/>
+      <x:c r="C18" s="99"/>
+      <x:c r="D18" s="99"/>
+      <x:c r="E18" s="99"/>
+      <x:c r="F18" s="99"/>
+      <x:c r="G18" s="99"/>
+      <x:c r="H18" s="99" t="str">
         <x:v>Stand</x:v>
       </x:c>
-      <x:c r="I16" s="41"/>
-      <x:c r="J16" s="41" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K16" s="41" t="str">
+      <x:c r="I18" s="99"/>
+      <x:c r="J18" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K18" s="99" t="str">
         <x:v>待机：主角 fd，怪物 zd</x:v>
       </x:c>
-      <x:c r="L16" s="41"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41" t="str">
+      <x:c r="L18" s="99"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="99"/>
+      <x:c r="B19" s="99"/>
+      <x:c r="C19" s="99"/>
+      <x:c r="D19" s="99"/>
+      <x:c r="E19" s="99"/>
+      <x:c r="F19" s="99"/>
+      <x:c r="G19" s="99"/>
+      <x:c r="H19" s="99" t="str">
         <x:v>Move</x:v>
       </x:c>
-      <x:c r="I17" s="41"/>
-      <x:c r="J17" s="41" t="n">
+      <x:c r="I19" s="99"/>
+      <x:c r="J19" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K17" s="41" t="str">
+      <x:c r="K19" s="99" t="str">
         <x:v>移动 pb</x:v>
       </x:c>
-      <x:c r="L17" s="41"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41" t="str">
+      <x:c r="L19" s="99"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="99"/>
+      <x:c r="B20" s="99"/>
+      <x:c r="C20" s="99"/>
+      <x:c r="D20" s="99"/>
+      <x:c r="E20" s="99"/>
+      <x:c r="F20" s="99"/>
+      <x:c r="G20" s="99"/>
+      <x:c r="H20" s="99" t="str">
         <x:v>Unused</x:v>
       </x:c>
-      <x:c r="I18" s="41"/>
-      <x:c r="J18" s="41" t="n">
+      <x:c r="I20" s="99"/>
+      <x:c r="J20" s="99" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K18" s="41" t="str">
+      <x:c r="K20" s="99" t="str">
         <x:v>本轮不使用的动作</x:v>
       </x:c>
-      <x:c r="L18" s="41"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="41"/>
-      <x:c r="B19" s="41"/>
-      <x:c r="C19" s="41"/>
-      <x:c r="D19" s="41"/>
-      <x:c r="E19" s="41"/>
-      <x:c r="F19" s="41"/>
-      <x:c r="G19" s="41"/>
-      <x:c r="H19" s="41" t="str">
+      <x:c r="L20" s="99"/>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="99"/>
+      <x:c r="B21" s="99"/>
+      <x:c r="C21" s="99"/>
+      <x:c r="D21" s="99"/>
+      <x:c r="E21" s="99"/>
+      <x:c r="F21" s="99"/>
+      <x:c r="G21" s="99"/>
+      <x:c r="H21" s="99" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="I19" s="41"/>
-      <x:c r="J19" s="41" t="n">
+      <x:c r="I21" s="99"/>
+      <x:c r="J21" s="99" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K19" s="41" t="str">
+      <x:c r="K21" s="99" t="str">
         <x:v>攻击 gj</x:v>
       </x:c>
-      <x:c r="L19" s="41"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="43"/>
-      <x:c r="B20" s="43"/>
-      <x:c r="C20" s="43"/>
-      <x:c r="D20" s="43"/>
-      <x:c r="E20" s="43"/>
-      <x:c r="F20" s="43"/>
-      <x:c r="G20" s="43"/>
-      <x:c r="H20" s="43" t="str">
+      <x:c r="L21" s="99"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="99"/>
+      <x:c r="B22" s="99"/>
+      <x:c r="C22" s="99"/>
+      <x:c r="D22" s="99"/>
+      <x:c r="E22" s="99"/>
+      <x:c r="F22" s="99"/>
+      <x:c r="G22" s="99"/>
+      <x:c r="H22" s="99" t="str">
         <x:v>Hit</x:v>
       </x:c>
-      <x:c r="I20" s="43"/>
-      <x:c r="J20" s="43" t="n">
+      <x:c r="I22" s="99"/>
+      <x:c r="J22" s="99" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K20" s="43" t="str">
+      <x:c r="K22" s="99" t="str">
         <x:v>被击 bj</x:v>
       </x:c>
-      <x:c r="L20" s="43"/>
-    </x:row>
-    <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="46"/>
-      <x:c r="B21" s="46"/>
-      <x:c r="C21" s="46"/>
-      <x:c r="D21" s="46"/>
-      <x:c r="E21" s="46"/>
-      <x:c r="F21" s="46"/>
-      <x:c r="G21" s="46"/>
-      <x:c r="H21" s="46" t="str">
+      <x:c r="L22" s="99"/>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="99"/>
+      <x:c r="B23" s="99"/>
+      <x:c r="C23" s="99"/>
+      <x:c r="D23" s="99"/>
+      <x:c r="E23" s="99"/>
+      <x:c r="F23" s="99"/>
+      <x:c r="G23" s="99"/>
+      <x:c r="H23" s="99" t="str">
         <x:v>Cast1</x:v>
       </x:c>
-      <x:c r="I21" s="46"/>
-      <x:c r="J21" s="46" t="n">
+      <x:c r="I23" s="99"/>
+      <x:c r="J23" s="99" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K21" s="48" t="str">
+      <x:c r="K23" s="99" t="str">
         <x:v>施法 sf1</x:v>
       </x:c>
-      <x:c r="L21" s="46"/>
-    </x:row>
-    <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="46"/>
-      <x:c r="B22" s="46"/>
-      <x:c r="C22" s="46"/>
-      <x:c r="D22" s="46"/>
-      <x:c r="E22" s="46"/>
-      <x:c r="F22" s="46"/>
-      <x:c r="G22" s="46"/>
-      <x:c r="H22" s="46" t="str">
+      <x:c r="L23" s="99"/>
+    </x:row>
+    <x:row r="24" ht="28" customHeight="1">
+      <x:c r="A24" s="99"/>
+      <x:c r="B24" s="99"/>
+      <x:c r="C24" s="99"/>
+      <x:c r="D24" s="99"/>
+      <x:c r="E24" s="99"/>
+      <x:c r="F24" s="99"/>
+      <x:c r="G24" s="99"/>
+      <x:c r="H24" s="99" t="str">
         <x:v>Cast2</x:v>
       </x:c>
-      <x:c r="I22" s="46"/>
-      <x:c r="J22" s="46" t="n">
+      <x:c r="I24" s="99"/>
+      <x:c r="J24" s="99" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K22" s="48" t="str">
+      <x:c r="K24" s="99" t="str">
         <x:v>施法 sf2</x:v>
       </x:c>
-      <x:c r="L22" s="46"/>
-    </x:row>
-    <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="46"/>
-      <x:c r="B23" s="46"/>
-      <x:c r="C23" s="46"/>
-      <x:c r="D23" s="46"/>
-      <x:c r="E23" s="46"/>
-      <x:c r="F23" s="46"/>
-      <x:c r="G23" s="46"/>
-      <x:c r="H23" s="46" t="str">
+      <x:c r="L24" s="99"/>
+    </x:row>
+    <x:row r="25" ht="28" customHeight="1">
+      <x:c r="A25" s="99"/>
+      <x:c r="B25" s="99"/>
+      <x:c r="C25" s="99"/>
+      <x:c r="D25" s="99"/>
+      <x:c r="E25" s="99"/>
+      <x:c r="F25" s="99"/>
+      <x:c r="G25" s="99"/>
+      <x:c r="H25" s="99" t="str">
         <x:v>Cast3</x:v>
       </x:c>
-      <x:c r="I23" s="46"/>
-      <x:c r="J23" s="46" t="n">
+      <x:c r="I25" s="99"/>
+      <x:c r="J25" s="99" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K23" s="48" t="str">
+      <x:c r="K25" s="99" t="str">
         <x:v>施法 sf3</x:v>
       </x:c>
-      <x:c r="L23" s="46"/>
-    </x:row>
-    <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="46"/>
-      <x:c r="B24" s="46"/>
-      <x:c r="C24" s="46"/>
-      <x:c r="D24" s="46"/>
-      <x:c r="E24" s="46"/>
-      <x:c r="F24" s="46"/>
-      <x:c r="G24" s="46"/>
-      <x:c r="H24" s="46" t="str">
+      <x:c r="L25" s="99"/>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
+      <x:c r="A26" s="99"/>
+      <x:c r="B26" s="99"/>
+      <x:c r="C26" s="99"/>
+      <x:c r="D26" s="99"/>
+      <x:c r="E26" s="99"/>
+      <x:c r="F26" s="99"/>
+      <x:c r="G26" s="99"/>
+      <x:c r="H26" s="99" t="str">
         <x:v>Cast4</x:v>
       </x:c>
-      <x:c r="I24" s="46"/>
-      <x:c r="J24" s="46" t="n">
+      <x:c r="I26" s="99"/>
+      <x:c r="J26" s="99" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K24" s="48" t="str">
+      <x:c r="K26" s="99" t="str">
         <x:v>施法 sf4</x:v>
       </x:c>
-      <x:c r="L24" s="46"/>
-    </x:row>
-    <x:row r="25" ht="28" customHeight="1">
-      <x:c r="A25" s="46"/>
-      <x:c r="B25" s="46"/>
-      <x:c r="C25" s="46"/>
-      <x:c r="D25" s="46"/>
-      <x:c r="E25" s="46"/>
-      <x:c r="F25" s="46"/>
-      <x:c r="G25" s="46"/>
-      <x:c r="H25" s="46" t="str">
+      <x:c r="L26" s="99"/>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
+      <x:c r="A27" s="99"/>
+      <x:c r="B27" s="99"/>
+      <x:c r="C27" s="99"/>
+      <x:c r="D27" s="99"/>
+      <x:c r="E27" s="99"/>
+      <x:c r="F27" s="99"/>
+      <x:c r="G27" s="99"/>
+      <x:c r="H27" s="99" t="str">
         <x:v>Death</x:v>
       </x:c>
-      <x:c r="I25" s="46"/>
-      <x:c r="J25" s="46" t="n">
+      <x:c r="I27" s="99"/>
+      <x:c r="J27" s="99" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K25" s="48" t="str">
+      <x:c r="K27" s="99" t="str">
         <x:v>死亡 sw</x:v>
       </x:c>
-      <x:c r="L25" s="46"/>
-    </x:row>
-    <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="46"/>
-      <x:c r="B26" s="46" t="str">
+      <x:c r="L27" s="99"/>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
+      <x:c r="A28" s="99"/>
+      <x:c r="B28" s="99"/>
+      <x:c r="C28" s="99"/>
+      <x:c r="D28" s="99"/>
+      <x:c r="E28" s="99"/>
+      <x:c r="F28" s="99"/>
+      <x:c r="G28" s="99"/>
+      <x:c r="H28" s="99" t="str">
+        <x:v>Projectile</x:v>
+      </x:c>
+      <x:c r="I28" s="99"/>
+      <x:c r="J28" s="99" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K28" s="99" t="str">
+        <x:v>弹丸飞行</x:v>
+      </x:c>
+      <x:c r="L28" s="99"/>
+    </x:row>
+    <x:row r="29" ht="28" customHeight="1">
+      <x:c r="A29" s="99"/>
+      <x:c r="B29" s="99"/>
+      <x:c r="C29" s="99"/>
+      <x:c r="D29" s="99"/>
+      <x:c r="E29" s="99"/>
+      <x:c r="F29" s="99"/>
+      <x:c r="G29" s="99"/>
+      <x:c r="H29" s="99" t="str">
+        <x:v>Impact</x:v>
+      </x:c>
+      <x:c r="I29" s="99"/>
+      <x:c r="J29" s="99" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K29" s="99" t="str">
+        <x:v>命中表现</x:v>
+      </x:c>
+      <x:c r="L29" s="99"/>
+    </x:row>
+    <x:row r="30" ht="28" customHeight="1">
+      <x:c r="A30" s="99"/>
+      <x:c r="B30" s="99"/>
+      <x:c r="C30" s="99"/>
+      <x:c r="D30" s="99"/>
+      <x:c r="E30" s="99"/>
+      <x:c r="F30" s="99"/>
+      <x:c r="G30" s="99"/>
+      <x:c r="H30" s="99" t="str">
+        <x:v>Area</x:v>
+      </x:c>
+      <x:c r="I30" s="99"/>
+      <x:c r="J30" s="99" t="str">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K30" s="99" t="str">
+        <x:v>目标位置范围表现</x:v>
+      </x:c>
+      <x:c r="L30" s="99"/>
+    </x:row>
+    <x:row r="31" ht="28" customHeight="1">
+      <x:c r="A31" s="99"/>
+      <x:c r="B31" s="99" t="str">
         <x:v>EPerformanceKind</x:v>
       </x:c>
-      <x:c r="C26" s="47" t="b">
+      <x:c r="C31" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D26" s="47" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E26" s="46"/>
-      <x:c r="F26" s="46"/>
-      <x:c r="G26" s="46"/>
-      <x:c r="H26" s="46" t="str">
+      <x:c r="D31" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="99"/>
+      <x:c r="F31" s="99"/>
+      <x:c r="G31" s="99"/>
+      <x:c r="H31" s="99" t="str">
         <x:v>SameMonster</x:v>
       </x:c>
-      <x:c r="I26" s="46"/>
-      <x:c r="J26" s="46" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K26" s="48" t="str">
+      <x:c r="I31" s="99"/>
+      <x:c r="J31" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K31" s="99" t="str">
         <x:v>同种怪物</x:v>
       </x:c>
-      <x:c r="L26" s="46"/>
-    </x:row>
-    <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="46"/>
-      <x:c r="B27" s="46"/>
-      <x:c r="C27" s="46"/>
-      <x:c r="D27" s="46"/>
-      <x:c r="E27" s="46"/>
-      <x:c r="F27" s="46"/>
-      <x:c r="G27" s="46"/>
-      <x:c r="H27" s="46" t="str">
+      <x:c r="L31" s="99"/>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
+      <x:c r="A32" s="99"/>
+      <x:c r="B32" s="99"/>
+      <x:c r="C32" s="99"/>
+      <x:c r="D32" s="99"/>
+      <x:c r="E32" s="99"/>
+      <x:c r="F32" s="99"/>
+      <x:c r="G32" s="99"/>
+      <x:c r="H32" s="99" t="str">
         <x:v>MixedMonsters</x:v>
       </x:c>
-      <x:c r="I27" s="46"/>
-      <x:c r="J27" s="46" t="n">
+      <x:c r="I32" s="99"/>
+      <x:c r="J32" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K27" s="48" t="str">
+      <x:c r="K32" s="99" t="str">
         <x:v>混合怪物</x:v>
       </x:c>
-      <x:c r="L27" s="46"/>
-    </x:row>
-    <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="46"/>
-      <x:c r="B28" s="46"/>
-      <x:c r="C28" s="46"/>
-      <x:c r="D28" s="46"/>
-      <x:c r="E28" s="46"/>
-      <x:c r="F28" s="46"/>
-      <x:c r="G28" s="46"/>
-      <x:c r="H28" s="46" t="str">
+      <x:c r="L32" s="99"/>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
+      <x:c r="A33" s="99"/>
+      <x:c r="B33" s="99"/>
+      <x:c r="C33" s="99"/>
+      <x:c r="D33" s="99"/>
+      <x:c r="E33" s="99"/>
+      <x:c r="F33" s="99"/>
+      <x:c r="G33" s="99"/>
+      <x:c r="H33" s="99" t="str">
         <x:v>MixedMonstersWithSkills</x:v>
       </x:c>
-      <x:c r="I28" s="46"/>
-      <x:c r="J28" s="46" t="n">
+      <x:c r="I33" s="99"/>
+      <x:c r="J33" s="99" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K28" s="48" t="str">
+      <x:c r="K33" s="99" t="str">
         <x:v>混合怪物与技能</x:v>
       </x:c>
-      <x:c r="L28" s="46"/>
-    </x:row>
-    <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="46"/>
-      <x:c r="B29" s="46"/>
-      <x:c r="C29" s="46"/>
-      <x:c r="D29" s="46"/>
-      <x:c r="E29" s="46"/>
-      <x:c r="F29" s="46"/>
-      <x:c r="G29" s="46"/>
-      <x:c r="H29" s="46" t="str">
+      <x:c r="L33" s="99"/>
+    </x:row>
+    <x:row r="34" ht="28" customHeight="1">
+      <x:c r="A34" s="99"/>
+      <x:c r="B34" s="99"/>
+      <x:c r="C34" s="99"/>
+      <x:c r="D34" s="99"/>
+      <x:c r="E34" s="99"/>
+      <x:c r="F34" s="99"/>
+      <x:c r="G34" s="99"/>
+      <x:c r="H34" s="99" t="str">
         <x:v>Combat</x:v>
       </x:c>
-      <x:c r="I29" s="46"/>
-      <x:c r="J29" s="46" t="n">
+      <x:c r="I34" s="99"/>
+      <x:c r="J34" s="99" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K29" s="48" t="str">
+      <x:c r="K34" s="99" t="str">
         <x:v>完整战斗测试</x:v>
       </x:c>
-      <x:c r="L29" s="46"/>
-    </x:row>
-    <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="46"/>
-      <x:c r="B30" s="46" t="str">
+      <x:c r="L34" s="99"/>
+    </x:row>
+    <x:row r="35" ht="28" customHeight="1">
+      <x:c r="A35" s="99"/>
+      <x:c r="B35" s="99" t="str">
         <x:v>EAttributeType</x:v>
       </x:c>
-      <x:c r="C30" s="47" t="b">
+      <x:c r="C35" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D30" s="47" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E30" s="46"/>
-      <x:c r="F30" s="46"/>
-      <x:c r="G30" s="46"/>
-      <x:c r="H30" s="46" t="str">
+      <x:c r="D35" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="99"/>
+      <x:c r="F35" s="99"/>
+      <x:c r="G35" s="99"/>
+      <x:c r="H35" s="99" t="str">
         <x:v>MaxHealth</x:v>
       </x:c>
-      <x:c r="I30" s="46"/>
-      <x:c r="J30" s="46" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K30" s="48" t="str">
+      <x:c r="I35" s="99"/>
+      <x:c r="J35" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K35" s="99" t="str">
         <x:v>最大生命</x:v>
       </x:c>
-      <x:c r="L30" s="46"/>
-    </x:row>
-    <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="46"/>
-      <x:c r="B31" s="46"/>
-      <x:c r="C31" s="46"/>
-      <x:c r="D31" s="46"/>
-      <x:c r="E31" s="46"/>
-      <x:c r="F31" s="46"/>
-      <x:c r="G31" s="46"/>
-      <x:c r="H31" s="46" t="str">
+      <x:c r="L35" s="99"/>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
+      <x:c r="A36" s="99"/>
+      <x:c r="B36" s="99"/>
+      <x:c r="C36" s="99"/>
+      <x:c r="D36" s="99"/>
+      <x:c r="E36" s="99"/>
+      <x:c r="F36" s="99"/>
+      <x:c r="G36" s="99"/>
+      <x:c r="H36" s="99" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="I31" s="46"/>
-      <x:c r="J31" s="46" t="n">
+      <x:c r="I36" s="99"/>
+      <x:c r="J36" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K31" s="48" t="str">
+      <x:c r="K36" s="99" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="L31" s="46"/>
-    </x:row>
-    <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="46"/>
-      <x:c r="B32" s="46"/>
-      <x:c r="C32" s="46"/>
-      <x:c r="D32" s="46"/>
-      <x:c r="E32" s="46"/>
-      <x:c r="F32" s="46"/>
-      <x:c r="G32" s="46"/>
-      <x:c r="H32" s="46" t="str">
+      <x:c r="L36" s="99"/>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
+      <x:c r="A37" s="99"/>
+      <x:c r="B37" s="99"/>
+      <x:c r="C37" s="99"/>
+      <x:c r="D37" s="99"/>
+      <x:c r="E37" s="99"/>
+      <x:c r="F37" s="99"/>
+      <x:c r="G37" s="99"/>
+      <x:c r="H37" s="99" t="str">
         <x:v>Defense</x:v>
       </x:c>
-      <x:c r="I32" s="46"/>
-      <x:c r="J32" s="46" t="n">
+      <x:c r="I37" s="99"/>
+      <x:c r="J37" s="99" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K32" s="48" t="str">
+      <x:c r="K37" s="99" t="str">
         <x:v>防御</x:v>
       </x:c>
-      <x:c r="L32" s="46"/>
-    </x:row>
-    <x:row r="33" ht="28" customHeight="1">
-      <x:c r="A33" s="46"/>
-      <x:c r="B33" s="46"/>
-      <x:c r="C33" s="46"/>
-      <x:c r="D33" s="46"/>
-      <x:c r="E33" s="46"/>
-      <x:c r="F33" s="46"/>
-      <x:c r="G33" s="46"/>
-      <x:c r="H33" s="46" t="str">
+      <x:c r="L37" s="99"/>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
+      <x:c r="A38" s="99"/>
+      <x:c r="B38" s="99"/>
+      <x:c r="C38" s="99"/>
+      <x:c r="D38" s="99"/>
+      <x:c r="E38" s="99"/>
+      <x:c r="F38" s="99"/>
+      <x:c r="G38" s="99"/>
+      <x:c r="H38" s="99" t="str">
         <x:v>MoveSpeed</x:v>
       </x:c>
-      <x:c r="I33" s="46"/>
-      <x:c r="J33" s="46" t="n">
+      <x:c r="I38" s="99"/>
+      <x:c r="J38" s="99" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K33" s="48" t="str">
+      <x:c r="K38" s="99" t="str">
         <x:v>移动速度</x:v>
       </x:c>
-      <x:c r="L33" s="46"/>
-    </x:row>
-    <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="46"/>
-      <x:c r="B34" s="46"/>
-      <x:c r="C34" s="46"/>
-      <x:c r="D34" s="46"/>
-      <x:c r="E34" s="46"/>
-      <x:c r="F34" s="46"/>
-      <x:c r="G34" s="46"/>
-      <x:c r="H34" s="46" t="str">
+      <x:c r="L38" s="99"/>
+    </x:row>
+    <x:row r="39" ht="28" customHeight="1">
+      <x:c r="A39" s="99"/>
+      <x:c r="B39" s="99"/>
+      <x:c r="C39" s="99"/>
+      <x:c r="D39" s="99"/>
+      <x:c r="E39" s="99"/>
+      <x:c r="F39" s="99"/>
+      <x:c r="G39" s="99"/>
+      <x:c r="H39" s="99" t="str">
         <x:v>AttackSpeedMultiplier</x:v>
       </x:c>
-      <x:c r="I34" s="46"/>
-      <x:c r="J34" s="46" t="n">
+      <x:c r="I39" s="99"/>
+      <x:c r="J39" s="99" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K34" s="48" t="str">
+      <x:c r="K39" s="99" t="str">
         <x:v>攻速倍率</x:v>
       </x:c>
-      <x:c r="L34" s="46"/>
-    </x:row>
-    <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="46"/>
-      <x:c r="B35" s="46"/>
-      <x:c r="C35" s="46"/>
-      <x:c r="D35" s="46"/>
-      <x:c r="E35" s="46"/>
-      <x:c r="F35" s="46"/>
-      <x:c r="G35" s="46"/>
-      <x:c r="H35" s="46" t="str">
+      <x:c r="L39" s="99"/>
+    </x:row>
+    <x:row r="40" ht="28" customHeight="1">
+      <x:c r="A40" s="99"/>
+      <x:c r="B40" s="99"/>
+      <x:c r="C40" s="99"/>
+      <x:c r="D40" s="99"/>
+      <x:c r="E40" s="99"/>
+      <x:c r="F40" s="99"/>
+      <x:c r="G40" s="99"/>
+      <x:c r="H40" s="99" t="str">
         <x:v>DefenseParameter</x:v>
       </x:c>
-      <x:c r="I35" s="46"/>
-      <x:c r="J35" s="46" t="n">
+      <x:c r="I40" s="99"/>
+      <x:c r="J40" s="99" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K35" s="48" t="str">
+      <x:c r="K40" s="99" t="str">
         <x:v>防御参数</x:v>
       </x:c>
-      <x:c r="L35" s="46"/>
-    </x:row>
-    <x:row r="36" ht="28" customHeight="1">
-      <x:c r="A36" s="46"/>
-      <x:c r="B36" s="46"/>
-      <x:c r="C36" s="46"/>
-      <x:c r="D36" s="46"/>
-      <x:c r="E36" s="46"/>
-      <x:c r="F36" s="46"/>
-      <x:c r="G36" s="46"/>
-      <x:c r="H36" s="46" t="str">
+      <x:c r="L40" s="99"/>
+    </x:row>
+    <x:row r="41" ht="48" customHeight="1">
+      <x:c r="A41" s="99"/>
+      <x:c r="B41" s="99"/>
+      <x:c r="C41" s="99"/>
+      <x:c r="D41" s="99"/>
+      <x:c r="E41" s="99"/>
+      <x:c r="F41" s="99"/>
+      <x:c r="G41" s="99"/>
+      <x:c r="H41" s="99" t="str">
         <x:v>Hit</x:v>
       </x:c>
-      <x:c r="I36" s="46"/>
-      <x:c r="J36" s="46" t="n">
+      <x:c r="I41" s="99"/>
+      <x:c r="J41" s="99" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K36" s="48" t="str">
+      <x:c r="K41" s="99" t="str">
         <x:v>命中值</x:v>
       </x:c>
-      <x:c r="L36" s="46"/>
-    </x:row>
-    <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="46"/>
-      <x:c r="B37" s="46"/>
-      <x:c r="C37" s="46"/>
-      <x:c r="D37" s="46"/>
-      <x:c r="E37" s="46"/>
-      <x:c r="F37" s="46"/>
-      <x:c r="G37" s="46"/>
-      <x:c r="H37" s="46" t="str">
+      <x:c r="L41" s="99"/>
+    </x:row>
+    <x:row r="42" ht="28" customHeight="1">
+      <x:c r="A42" s="99"/>
+      <x:c r="B42" s="99"/>
+      <x:c r="C42" s="99"/>
+      <x:c r="D42" s="99"/>
+      <x:c r="E42" s="99"/>
+      <x:c r="F42" s="99"/>
+      <x:c r="G42" s="99"/>
+      <x:c r="H42" s="99" t="str">
         <x:v>Evasion</x:v>
       </x:c>
-      <x:c r="I37" s="46"/>
-      <x:c r="J37" s="46" t="n">
+      <x:c r="I42" s="99"/>
+      <x:c r="J42" s="99" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K37" s="48" t="str">
+      <x:c r="K42" s="99" t="str">
         <x:v>闪避值</x:v>
       </x:c>
-      <x:c r="L37" s="46"/>
-    </x:row>
-    <x:row r="38" ht="28" customHeight="1">
-      <x:c r="A38" s="46"/>
-      <x:c r="B38" s="46"/>
-      <x:c r="C38" s="46"/>
-      <x:c r="D38" s="46"/>
-      <x:c r="E38" s="46"/>
-      <x:c r="F38" s="46"/>
-      <x:c r="G38" s="46"/>
-      <x:c r="H38" s="46" t="str">
+      <x:c r="L42" s="99"/>
+    </x:row>
+    <x:row r="43" ht="28" customHeight="1">
+      <x:c r="A43" s="99"/>
+      <x:c r="B43" s="99"/>
+      <x:c r="C43" s="99"/>
+      <x:c r="D43" s="99"/>
+      <x:c r="E43" s="99"/>
+      <x:c r="F43" s="99"/>
+      <x:c r="G43" s="99"/>
+      <x:c r="H43" s="99" t="str">
         <x:v>HitParameter</x:v>
       </x:c>
-      <x:c r="I38" s="46"/>
-      <x:c r="J38" s="46" t="n">
+      <x:c r="I43" s="99"/>
+      <x:c r="J43" s="99" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K38" s="48" t="str">
+      <x:c r="K43" s="99" t="str">
         <x:v>命中参数</x:v>
       </x:c>
-      <x:c r="L38" s="46"/>
-    </x:row>
-    <x:row r="39" ht="28" customHeight="1">
-      <x:c r="A39" s="46"/>
-      <x:c r="B39" s="46"/>
-      <x:c r="C39" s="46"/>
-      <x:c r="D39" s="46"/>
-      <x:c r="E39" s="46"/>
-      <x:c r="F39" s="46"/>
-      <x:c r="G39" s="46"/>
-      <x:c r="H39" s="46" t="str">
+      <x:c r="L43" s="99"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="99"/>
+      <x:c r="B44" s="99"/>
+      <x:c r="C44" s="99"/>
+      <x:c r="D44" s="99"/>
+      <x:c r="E44" s="99"/>
+      <x:c r="F44" s="99"/>
+      <x:c r="G44" s="99"/>
+      <x:c r="H44" s="99" t="str">
         <x:v>EvasionParameter</x:v>
       </x:c>
-      <x:c r="I39" s="46"/>
-      <x:c r="J39" s="46" t="n">
+      <x:c r="I44" s="99"/>
+      <x:c r="J44" s="99" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K39" s="48" t="str">
+      <x:c r="K44" s="99" t="str">
         <x:v>闪避参数</x:v>
       </x:c>
-      <x:c r="L39" s="46"/>
-    </x:row>
-    <x:row r="40" ht="28" customHeight="1">
-      <x:c r="A40" s="46"/>
-      <x:c r="B40" s="46"/>
-      <x:c r="C40" s="46"/>
-      <x:c r="D40" s="46"/>
-      <x:c r="E40" s="46"/>
-      <x:c r="F40" s="46"/>
-      <x:c r="G40" s="46"/>
-      <x:c r="H40" s="46" t="str">
+      <x:c r="L44" s="99"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="99"/>
+      <x:c r="B45" s="99"/>
+      <x:c r="C45" s="99"/>
+      <x:c r="D45" s="99"/>
+      <x:c r="E45" s="99"/>
+      <x:c r="F45" s="99"/>
+      <x:c r="G45" s="99"/>
+      <x:c r="H45" s="99" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="I40" s="46"/>
-      <x:c r="J40" s="46" t="n">
+      <x:c r="I45" s="99"/>
+      <x:c r="J45" s="99" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K40" s="48" t="str">
+      <x:c r="K45" s="99" t="str">
         <x:v>暴击值</x:v>
       </x:c>
-      <x:c r="L40" s="46"/>
-    </x:row>
-    <x:row r="41" ht="48" customHeight="1">
-      <x:c r="A41" s="46"/>
-      <x:c r="B41" s="46"/>
-      <x:c r="C41" s="46"/>
-      <x:c r="D41" s="46"/>
-      <x:c r="E41" s="46"/>
-      <x:c r="F41" s="46"/>
-      <x:c r="G41" s="46"/>
-      <x:c r="H41" s="46" t="str">
+      <x:c r="L45" s="99"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="99"/>
+      <x:c r="B46" s="99"/>
+      <x:c r="C46" s="99"/>
+      <x:c r="D46" s="99"/>
+      <x:c r="E46" s="99"/>
+      <x:c r="F46" s="99"/>
+      <x:c r="G46" s="99"/>
+      <x:c r="H46" s="99" t="str">
         <x:v>CriticalResistance</x:v>
       </x:c>
-      <x:c r="I41" s="46"/>
-      <x:c r="J41" s="46" t="n">
+      <x:c r="I46" s="99"/>
+      <x:c r="J46" s="99" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K41" s="48" t="str">
+      <x:c r="K46" s="99" t="str">
         <x:v>抗暴值</x:v>
       </x:c>
-      <x:c r="L41" s="46"/>
-    </x:row>
-    <x:row r="42" ht="28" customHeight="1">
-      <x:c r="A42" s="46"/>
-      <x:c r="B42" s="46"/>
-      <x:c r="C42" s="46"/>
-      <x:c r="D42" s="46"/>
-      <x:c r="E42" s="46"/>
-      <x:c r="F42" s="46"/>
-      <x:c r="G42" s="46"/>
-      <x:c r="H42" s="46" t="str">
+      <x:c r="L46" s="99"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="99"/>
+      <x:c r="B47" s="99"/>
+      <x:c r="C47" s="99"/>
+      <x:c r="D47" s="99"/>
+      <x:c r="E47" s="99"/>
+      <x:c r="F47" s="99"/>
+      <x:c r="G47" s="99"/>
+      <x:c r="H47" s="99" t="str">
         <x:v>CriticalParameter</x:v>
       </x:c>
-      <x:c r="I42" s="46"/>
-      <x:c r="J42" s="46" t="n">
+      <x:c r="I47" s="99"/>
+      <x:c r="J47" s="99" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K42" s="48" t="str">
+      <x:c r="K47" s="99" t="str">
         <x:v>暴击参数</x:v>
       </x:c>
-      <x:c r="L42" s="46"/>
-    </x:row>
-    <x:row r="43" ht="28" customHeight="1">
-      <x:c r="A43" s="46"/>
-      <x:c r="B43" s="46"/>
-      <x:c r="C43" s="46"/>
-      <x:c r="D43" s="46"/>
-      <x:c r="E43" s="46"/>
-      <x:c r="F43" s="46"/>
-      <x:c r="G43" s="46"/>
-      <x:c r="H43" s="46" t="str">
+      <x:c r="L47" s="99"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="99"/>
+      <x:c r="B48" s="99"/>
+      <x:c r="C48" s="99"/>
+      <x:c r="D48" s="99"/>
+      <x:c r="E48" s="99"/>
+      <x:c r="F48" s="99"/>
+      <x:c r="G48" s="99"/>
+      <x:c r="H48" s="99" t="str">
         <x:v>CriticalResistanceParameter</x:v>
       </x:c>
-      <x:c r="I43" s="46"/>
-      <x:c r="J43" s="46" t="n">
+      <x:c r="I48" s="99"/>
+      <x:c r="J48" s="99" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K43" s="48" t="str">
+      <x:c r="K48" s="99" t="str">
         <x:v>抗暴参数</x:v>
       </x:c>
-      <x:c r="L43" s="46"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44"/>
-      <x:c r="B44" t="str">
+      <x:c r="L48" s="99"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="99"/>
+      <x:c r="B49" s="99" t="str">
         <x:v>EAttributeValueKind</x:v>
       </x:c>
-      <x:c r="C44" s="1" t="b">
+      <x:c r="C49" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E44"/>
-      <x:c r="F44"/>
-      <x:c r="G44"/>
-      <x:c r="H44" t="str">
+      <x:c r="D49" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E49" s="99"/>
+      <x:c r="F49" s="99"/>
+      <x:c r="G49" s="99"/>
+      <x:c r="H49" s="99" t="str">
         <x:v>Integer</x:v>
       </x:c>
-      <x:c r="I44"/>
-      <x:c r="J44" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K44" t="str">
+      <x:c r="I49" s="99"/>
+      <x:c r="J49" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K49" s="99" t="str">
         <x:v>整数</x:v>
       </x:c>
-      <x:c r="L44"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45"/>
-      <x:c r="B45"/>
-      <x:c r="C45"/>
-      <x:c r="D45"/>
-      <x:c r="E45"/>
-      <x:c r="F45"/>
-      <x:c r="G45"/>
-      <x:c r="H45" t="str">
+      <x:c r="L49" s="99"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="99"/>
+      <x:c r="B50" s="99"/>
+      <x:c r="C50" s="99"/>
+      <x:c r="D50" s="99"/>
+      <x:c r="E50" s="99"/>
+      <x:c r="F50" s="99"/>
+      <x:c r="G50" s="99"/>
+      <x:c r="H50" s="99" t="str">
         <x:v>Real</x:v>
       </x:c>
-      <x:c r="I45"/>
-      <x:c r="J45" t="n">
+      <x:c r="I50" s="99"/>
+      <x:c r="J50" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K45" t="str">
+      <x:c r="K50" s="99" t="str">
         <x:v>实数</x:v>
       </x:c>
-      <x:c r="L45"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46"/>
-      <x:c r="B46" t="str">
+      <x:c r="L50" s="99"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="99"/>
+      <x:c r="B51" s="99" t="str">
         <x:v>ESkillDeliveryType</x:v>
       </x:c>
-      <x:c r="C46" s="1" t="b">
+      <x:c r="C51" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E46"/>
-      <x:c r="F46"/>
-      <x:c r="G46"/>
-      <x:c r="H46" t="str">
+      <x:c r="D51" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E51" s="99"/>
+      <x:c r="F51" s="99"/>
+      <x:c r="G51" s="99"/>
+      <x:c r="H51" s="99" t="str">
         <x:v>Projectile</x:v>
       </x:c>
-      <x:c r="I46"/>
-      <x:c r="J46" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K46" t="str">
+      <x:c r="I51" s="99"/>
+      <x:c r="J51" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K51" s="99" t="str">
         <x:v>直线弹丸</x:v>
       </x:c>
-      <x:c r="L46"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47"/>
-      <x:c r="B47"/>
-      <x:c r="C47"/>
-      <x:c r="D47"/>
-      <x:c r="E47"/>
-      <x:c r="F47"/>
-      <x:c r="G47"/>
-      <x:c r="H47" t="str">
+      <x:c r="L51" s="99"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="99"/>
+      <x:c r="B52" s="99"/>
+      <x:c r="C52" s="99"/>
+      <x:c r="D52" s="99"/>
+      <x:c r="E52" s="99"/>
+      <x:c r="F52" s="99"/>
+      <x:c r="G52" s="99"/>
+      <x:c r="H52" s="99" t="str">
         <x:v>Melee</x:v>
       </x:c>
-      <x:c r="I47"/>
-      <x:c r="J47" t="n">
+      <x:c r="I52" s="99"/>
+      <x:c r="J52" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K47" t="str">
+      <x:c r="K52" s="99" t="str">
         <x:v>近战</x:v>
       </x:c>
-      <x:c r="L47"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48"/>
-      <x:c r="B48" t="str">
+      <x:c r="L52" s="99"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="99"/>
+      <x:c r="B53" s="99"/>
+      <x:c r="C53" s="99"/>
+      <x:c r="D53" s="99"/>
+      <x:c r="E53" s="99"/>
+      <x:c r="F53" s="99"/>
+      <x:c r="G53" s="99"/>
+      <x:c r="H53" s="99" t="str">
+        <x:v>TargetArea</x:v>
+      </x:c>
+      <x:c r="I53" s="99"/>
+      <x:c r="J53" s="99" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K53" s="99" t="str">
+        <x:v>目标位置群体释放</x:v>
+      </x:c>
+      <x:c r="L53" s="99"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="99"/>
+      <x:c r="B54" s="99" t="str">
         <x:v>ETestHealthPolicy</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="b">
+      <x:c r="C54" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E48"/>
-      <x:c r="F48"/>
-      <x:c r="G48"/>
-      <x:c r="H48" t="str">
+      <x:c r="D54" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" s="99"/>
+      <x:c r="F54" s="99"/>
+      <x:c r="G54" s="99"/>
+      <x:c r="H54" s="99" t="str">
         <x:v>Normal</x:v>
       </x:c>
-      <x:c r="I48"/>
-      <x:c r="J48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K48" t="str">
+      <x:c r="I54" s="99"/>
+      <x:c r="J54" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K54" s="99" t="str">
         <x:v>正常生命</x:v>
       </x:c>
-      <x:c r="L48"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49"/>
-      <x:c r="B49"/>
-      <x:c r="C49"/>
-      <x:c r="D49"/>
-      <x:c r="E49"/>
-      <x:c r="F49"/>
-      <x:c r="G49"/>
-      <x:c r="H49" t="str">
+      <x:c r="L54" s="99"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="99"/>
+      <x:c r="B55" s="99"/>
+      <x:c r="C55" s="99"/>
+      <x:c r="D55" s="99"/>
+      <x:c r="E55" s="99"/>
+      <x:c r="F55" s="99"/>
+      <x:c r="G55" s="99"/>
+      <x:c r="H55" s="99" t="str">
         <x:v>RestoreAfterDamage</x:v>
       </x:c>
-      <x:c r="I49"/>
-      <x:c r="J49" t="n">
+      <x:c r="I55" s="99"/>
+      <x:c r="J55" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K49" t="str">
+      <x:c r="K55" s="99" t="str">
         <x:v>结算正数扣血后恢复测试玩家生命</x:v>
       </x:c>
-      <x:c r="L49"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50"/>
-      <x:c r="B50" t="str">
+      <x:c r="L55" s="99"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="99"/>
+      <x:c r="B56" s="99" t="str">
         <x:v>ETestInputPolicy</x:v>
       </x:c>
-      <x:c r="C50" s="1" t="b">
+      <x:c r="C56" s="100" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D50" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E50"/>
-      <x:c r="F50"/>
-      <x:c r="G50"/>
-      <x:c r="H50" t="str">
+      <x:c r="D56" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E56" s="99"/>
+      <x:c r="F56" s="99"/>
+      <x:c r="G56" s="99"/>
+      <x:c r="H56" s="99" t="str">
         <x:v>Manual</x:v>
       </x:c>
-      <x:c r="I50"/>
-      <x:c r="J50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K50" t="str">
+      <x:c r="I56" s="99"/>
+      <x:c r="J56" s="99" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K56" s="99" t="str">
         <x:v>玩家操作</x:v>
       </x:c>
-      <x:c r="L50"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51"/>
-      <x:c r="B51"/>
-      <x:c r="C51"/>
-      <x:c r="D51"/>
-      <x:c r="E51"/>
-      <x:c r="F51"/>
-      <x:c r="G51"/>
-      <x:c r="H51" t="str">
+      <x:c r="L56" s="99"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="99"/>
+      <x:c r="B57" s="99"/>
+      <x:c r="C57" s="99"/>
+      <x:c r="D57" s="99"/>
+      <x:c r="E57" s="99"/>
+      <x:c r="F57" s="99"/>
+      <x:c r="G57" s="99"/>
+      <x:c r="H57" s="99" t="str">
         <x:v>Stationary</x:v>
       </x:c>
-      <x:c r="I51"/>
-      <x:c r="J51" t="n">
+      <x:c r="I57" s="99"/>
+      <x:c r="J57" s="99" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K51" t="str">
+      <x:c r="K57" s="99" t="str">
         <x:v>玩家静止</x:v>
       </x:c>
-      <x:c r="L51"/>
+      <x:c r="L57" s="99"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="99"/>
+      <x:c r="B58" s="99" t="str">
+        <x:v>EMovementType</x:v>
+      </x:c>
+      <x:c r="C58" s="100" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D58" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E58" s="99"/>
+      <x:c r="F58" s="99" t="str">
+        <x:v>单位移动分类</x:v>
+      </x:c>
+      <x:c r="G58" s="99"/>
+      <x:c r="H58" s="99" t="str">
+        <x:v>Ground</x:v>
+      </x:c>
+      <x:c r="I58" s="99"/>
+      <x:c r="J58" s="99" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K58" s="99" t="str">
+        <x:v>地面</x:v>
+      </x:c>
+      <x:c r="L58" s="99"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="99"/>
+      <x:c r="B59" s="99"/>
+      <x:c r="C59" s="99"/>
+      <x:c r="D59" s="99"/>
+      <x:c r="E59" s="99"/>
+      <x:c r="F59" s="99"/>
+      <x:c r="G59" s="99"/>
+      <x:c r="H59" s="99" t="str">
+        <x:v>Flying</x:v>
+      </x:c>
+      <x:c r="I59" s="99"/>
+      <x:c r="J59" s="99" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K59" s="99" t="str">
+        <x:v>飞行</x:v>
+      </x:c>
+      <x:c r="L59" s="99"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="99"/>
+      <x:c r="B60" s="99" t="str">
+        <x:v>EUpgradeOptionType</x:v>
+      </x:c>
+      <x:c r="C60" s="100" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D60" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E60" s="99"/>
+      <x:c r="F60" s="99" t="str">
+        <x:v>局内升级选项类型</x:v>
+      </x:c>
+      <x:c r="G60" s="99"/>
+      <x:c r="H60" s="99" t="str">
+        <x:v>SkillUnlock</x:v>
+      </x:c>
+      <x:c r="I60" s="99"/>
+      <x:c r="J60" s="99" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K60" s="99" t="str">
+        <x:v>解锁技能</x:v>
+      </x:c>
+      <x:c r="L60" s="99"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="99"/>
+      <x:c r="B61" s="99"/>
+      <x:c r="C61" s="99"/>
+      <x:c r="D61" s="99"/>
+      <x:c r="E61" s="99"/>
+      <x:c r="F61" s="99"/>
+      <x:c r="G61" s="99"/>
+      <x:c r="H61" s="99" t="str">
+        <x:v>Attribute</x:v>
+      </x:c>
+      <x:c r="I61" s="99"/>
+      <x:c r="J61" s="99" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K61" s="99" t="str">
+        <x:v>属性强化</x:v>
+      </x:c>
+      <x:c r="L61" s="99"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="99"/>
+      <x:c r="B62" s="99"/>
+      <x:c r="C62" s="99"/>
+      <x:c r="D62" s="99"/>
+      <x:c r="E62" s="99"/>
+      <x:c r="F62" s="99"/>
+      <x:c r="G62" s="99"/>
+      <x:c r="H62" s="99" t="str">
+        <x:v>Heal</x:v>
+      </x:c>
+      <x:c r="I62" s="99"/>
+      <x:c r="J62" s="99" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K62" s="99" t="str">
+        <x:v>立即恢复</x:v>
+      </x:c>
+      <x:c r="L62" s="99"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="99"/>
+      <x:c r="B63" s="99" t="str">
+        <x:v>EAttributeModifyOperation</x:v>
+      </x:c>
+      <x:c r="C63" s="100" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D63" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E63" s="99"/>
+      <x:c r="F63" s="99" t="str">
+        <x:v>局内属性修改操作</x:v>
+      </x:c>
+      <x:c r="G63" s="99"/>
+      <x:c r="H63" s="99" t="str">
+        <x:v>Add</x:v>
+      </x:c>
+      <x:c r="I63" s="99"/>
+      <x:c r="J63" s="99" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K63" s="99" t="str">
+        <x:v>固定值相加</x:v>
+      </x:c>
+      <x:c r="L63" s="99"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="99"/>
+      <x:c r="B64" s="99"/>
+      <x:c r="C64" s="99"/>
+      <x:c r="D64" s="99"/>
+      <x:c r="E64" s="99"/>
+      <x:c r="F64" s="99"/>
+      <x:c r="G64" s="99"/>
+      <x:c r="H64" s="99" t="str">
+        <x:v>AddPercent</x:v>
+      </x:c>
+      <x:c r="I64" s="99"/>
+      <x:c r="J64" s="99" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K64" s="99" t="str">
+        <x:v>基础值百分比相加</x:v>
+      </x:c>
+      <x:c r="L64" s="99"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="99"/>
+      <x:c r="B65" s="99"/>
+      <x:c r="C65" s="99"/>
+      <x:c r="D65" s="99"/>
+      <x:c r="E65" s="99"/>
+      <x:c r="F65" s="99"/>
+      <x:c r="G65" s="99"/>
+      <x:c r="H65" s="99" t="str">
+        <x:v>Multiply</x:v>
+      </x:c>
+      <x:c r="I65" s="99"/>
+      <x:c r="J65" s="99" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K65" s="99" t="str">
+        <x:v>最终值相乘</x:v>
+      </x:c>
+      <x:c r="L65" s="99"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="99"/>
+      <x:c r="B66" s="99" t="str">
+        <x:v>ERunResultType</x:v>
+      </x:c>
+      <x:c r="C66" s="100" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D66" s="100" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E66" s="99"/>
+      <x:c r="F66" s="99" t="str">
+        <x:v>单局结算结果</x:v>
+      </x:c>
+      <x:c r="G66" s="99"/>
+      <x:c r="H66" s="99" t="str">
+        <x:v>Victory</x:v>
+      </x:c>
+      <x:c r="I66" s="99"/>
+      <x:c r="J66" s="99" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K66" s="99" t="str">
+        <x:v>胜利</x:v>
+      </x:c>
+      <x:c r="L66" s="99"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="99"/>
+      <x:c r="B67" s="99"/>
+      <x:c r="C67" s="99"/>
+      <x:c r="D67" s="99"/>
+      <x:c r="E67" s="99"/>
+      <x:c r="F67" s="99"/>
+      <x:c r="G67" s="99"/>
+      <x:c r="H67" s="99" t="str">
+        <x:v>Defeat</x:v>
+      </x:c>
+      <x:c r="I67" s="99"/>
+      <x:c r="J67" s="99" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K67" s="99" t="str">
+        <x:v>失败</x:v>
+      </x:c>
+      <x:c r="L67" s="99"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R19f691d8a10c4d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="Rc1cd44ec50a249be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2369,6 +2369,26 @@
       </x:c>
       <x:c r="L67" s="99"/>
     </x:row>
+    <x:row r="69">
+      <x:c r="A69"/>
+      <x:c r="B69" t="str">
+        <x:v>EUnitCollisionShape</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E69"/>
+      <x:c r="F69" t="str">
+        <x:v>单位统一碰撞形状</x:v>
+      </x:c>
+      <x:c r="G69"/>
+      <x:c r="H69" t="str">
+        <x:v>VerticalCapsule</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>
